--- a/Design Files/LightSPT-Device-v1.0/BOM/eSpark_BOM_Light_spt_device.xlsx
+++ b/Design Files/LightSPT-Device-v1.0/BOM/eSpark_BOM_Light_spt_device.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\chrisbyrd-lightsptdevice\Design Files\Light_spt_device\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\chrisbyrd-lightsptdevice\Design Files\LightSPT-Device-v1.0\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="389">
   <si>
     <t>Component list</t>
   </si>
@@ -72,9 +72,6 @@
     <t>Pogo Connector</t>
   </si>
   <si>
-    <t>SMA</t>
-  </si>
-  <si>
     <t>SIM Card Connectors</t>
   </si>
   <si>
@@ -384,18 +381,12 @@
     <t>Pogo Pad 2.5mm 4 Pin</t>
   </si>
   <si>
-    <t>1 Inner bore SMA Board Edge Bend -55℃~+155℃ 50Ω Plugin RF Connectors / Coaxial Connectors ROHS</t>
-  </si>
-  <si>
     <t>Copper Alloy Self bomb Gold plating 1.25mm Deck -40℃~+85℃ 260℃ NanoSIM SMD SIM Card Connectors ROHS</t>
   </si>
   <si>
     <t>RELAY GEN PURPOSE SPDT 3A 3V</t>
   </si>
   <si>
-    <t>FIXED IND 10UH 2.5A 43.7 MOHM</t>
-  </si>
-  <si>
     <t>2.7A 6.8uH ±20% 50mΩ SMD Power Inductors ROHS</t>
   </si>
   <si>
@@ -675,12 +666,6 @@
     <t>POGO Connector 4 Pin</t>
   </si>
   <si>
-    <t>HJ-SMA508</t>
-  </si>
-  <si>
-    <t>SLF10145T-100M2R5-PF</t>
-  </si>
-  <si>
     <t>LVC505040-6R8M-N</t>
   </si>
   <si>
@@ -825,9 +810,6 @@
     <t>BOOMELE</t>
   </si>
   <si>
-    <t>HJ Tech</t>
-  </si>
-  <si>
     <t>XKB Connectivity</t>
   </si>
   <si>
@@ -948,15 +930,9 @@
     <t>C430602</t>
   </si>
   <si>
-    <t>C1509209</t>
-  </si>
-  <si>
     <t>C381071</t>
   </si>
   <si>
-    <t>C96116</t>
-  </si>
-  <si>
     <t>C285870</t>
   </si>
   <si>
@@ -1186,6 +1162,30 @@
   </si>
   <si>
     <t>DO NOT MOUNT</t>
+  </si>
+  <si>
+    <t>FIXED IND 10UH 2.5A 79.3MOHM SMD</t>
+  </si>
+  <si>
+    <t>VLS5045EX-100M-H</t>
+  </si>
+  <si>
+    <t>C1845361</t>
+  </si>
+  <si>
+    <t>Sma Female Connector, Pcb Edge Mount Rohs Compliant: Yes</t>
+  </si>
+  <si>
+    <t>CON-SMA-EDGE_S</t>
+  </si>
+  <si>
+    <t>CON-SMA-EDGE-S</t>
+  </si>
+  <si>
+    <t>RF Solutions</t>
+  </si>
+  <si>
+    <t>SMA Connector</t>
   </si>
 </sst>
 </file>
@@ -1827,6 +1827,59 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1858,59 +1911,6 @@
     <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2288,15 +2288,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="61"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+      <c r="S1" s="80"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2346,7 +2346,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="62"/>
+      <c r="S3" s="81"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2371,7 +2371,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="63"/>
+      <c r="S4" s="82"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2396,7 +2396,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="63"/>
+      <c r="S5" s="82"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2417,7 +2417,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="63"/>
+      <c r="S6" s="82"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2438,7 +2438,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="63"/>
+      <c r="S7" s="82"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2459,7 +2459,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="63"/>
+      <c r="S8" s="82"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2470,52 +2470,52 @@
         <v>8</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>278</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>357</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>353</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>358</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>359</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>360</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>362</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>363</v>
+      </c>
+      <c r="S9" s="30" t="s">
         <v>364</v>
-      </c>
-      <c r="J9" s="30" t="s">
-        <v>284</v>
-      </c>
-      <c r="K9" s="30" t="s">
-        <v>365</v>
-      </c>
-      <c r="L9" s="30" t="s">
-        <v>361</v>
-      </c>
-      <c r="M9" s="30" t="s">
-        <v>366</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>367</v>
-      </c>
-      <c r="O9" s="30" t="s">
-        <v>368</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>369</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>370</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>371</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -2527,52 +2527,52 @@
       <c r="C10" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="74" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74" t="s">
-        <v>374</v>
-      </c>
-      <c r="G10" s="74" t="s">
-        <v>155</v>
-      </c>
-      <c r="H10" s="74" t="s">
-        <v>373</v>
-      </c>
-      <c r="I10" s="74" t="s">
-        <v>373</v>
-      </c>
-      <c r="J10" s="74" t="s">
-        <v>373</v>
-      </c>
-      <c r="K10" s="74" t="s">
-        <v>373</v>
-      </c>
-      <c r="L10" s="74">
+      <c r="D10" s="64" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64" t="s">
+        <v>366</v>
+      </c>
+      <c r="G10" s="64" t="s">
+        <v>152</v>
+      </c>
+      <c r="H10" s="64" t="s">
+        <v>365</v>
+      </c>
+      <c r="I10" s="64" t="s">
+        <v>365</v>
+      </c>
+      <c r="J10" s="64" t="s">
+        <v>365</v>
+      </c>
+      <c r="K10" s="64" t="s">
+        <v>365</v>
+      </c>
+      <c r="L10" s="64">
         <v>1</v>
       </c>
-      <c r="M10" s="74">
+      <c r="M10" s="64">
         <f>L10*5</f>
         <v>5</v>
       </c>
-      <c r="N10" s="74" t="s">
-        <v>373</v>
-      </c>
-      <c r="O10" s="74" t="s">
-        <v>373</v>
-      </c>
-      <c r="P10" s="87" t="s">
-        <v>373</v>
-      </c>
-      <c r="Q10" s="87" t="s">
-        <v>373</v>
-      </c>
-      <c r="R10" s="74"/>
+      <c r="N10" s="64" t="s">
+        <v>365</v>
+      </c>
+      <c r="O10" s="64" t="s">
+        <v>365</v>
+      </c>
+      <c r="P10" s="77" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q10" s="77" t="s">
+        <v>365</v>
+      </c>
+      <c r="R10" s="64"/>
       <c r="S10" s="50"/>
     </row>
-    <row r="11" spans="1:19" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="71"/>
+    <row r="11" spans="1:19" s="62" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="61"/>
       <c r="B11" s="47">
         <f t="shared" ref="B11:B71" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
@@ -2581,28 +2581,28 @@
         <v>9</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="I11" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J11" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="K11" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
@@ -2614,8 +2614,8 @@
       <c r="N11" s="51">
         <v>6</v>
       </c>
-      <c r="O11" s="70" t="s">
-        <v>375</v>
+      <c r="O11" s="60" t="s">
+        <v>367</v>
       </c>
       <c r="P11" s="38">
         <v>1.59</v>
@@ -2637,28 +2637,28 @@
         <v>10</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="L12" s="37">
         <v>23</v>
@@ -2670,8 +2670,8 @@
       <c r="N12" s="37">
         <v>150</v>
       </c>
-      <c r="O12" s="73" t="s">
-        <v>376</v>
+      <c r="O12" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P12" s="38">
         <v>1.0500000000000001E-2</v>
@@ -2693,28 +2693,28 @@
         <v>10</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="I13" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="L13" s="51">
         <v>3</v>
@@ -2726,8 +2726,8 @@
       <c r="N13" s="51">
         <v>50</v>
       </c>
-      <c r="O13" s="73" t="s">
-        <v>376</v>
+      <c r="O13" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P13" s="52">
         <v>1.0800000000000001E-2</v>
@@ -2749,28 +2749,28 @@
         <v>10</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L14" s="37">
         <v>1</v>
@@ -2782,8 +2782,8 @@
       <c r="N14" s="37">
         <v>100</v>
       </c>
-      <c r="O14" s="70" t="s">
-        <v>376</v>
+      <c r="O14" s="60" t="s">
+        <v>368</v>
       </c>
       <c r="P14" s="38">
         <v>2.2000000000000001E-3</v>
@@ -2805,26 +2805,26 @@
         <v>10</v>
       </c>
       <c r="D15" s="51" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G15" s="51" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H15" s="51" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="I15" s="51"/>
       <c r="J15" s="51" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="L15" s="51">
         <v>4</v>
@@ -2836,8 +2836,8 @@
       <c r="N15" s="51">
         <v>21</v>
       </c>
-      <c r="O15" s="73" t="s">
-        <v>376</v>
+      <c r="O15" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P15" s="52">
         <v>0.39779999999999999</v>
@@ -2859,28 +2859,28 @@
         <v>10</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="G16" s="74" t="s">
-        <v>196</v>
+        <v>154</v>
+      </c>
+      <c r="G16" s="64" t="s">
+        <v>193</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="L16" s="37">
         <v>5</v>
@@ -2892,8 +2892,8 @@
       <c r="N16" s="37">
         <v>30</v>
       </c>
-      <c r="O16" s="73" t="s">
-        <v>376</v>
+      <c r="O16" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P16" s="38">
         <v>3.7199999999999997E-2</v>
@@ -2915,28 +2915,28 @@
         <v>10</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H17" s="51" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I17" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J17" s="51" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="L17" s="51">
         <v>2</v>
@@ -2948,8 +2948,8 @@
       <c r="N17" s="51">
         <v>100</v>
       </c>
-      <c r="O17" s="73" t="s">
-        <v>376</v>
+      <c r="O17" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P17" s="52">
         <v>8.9999999999999998E-4</v>
@@ -2971,28 +2971,28 @@
         <v>10</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="K18" s="37" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="L18" s="37">
         <v>5</v>
@@ -3004,8 +3004,8 @@
       <c r="N18" s="37">
         <v>100</v>
       </c>
-      <c r="O18" s="70" t="s">
-        <v>376</v>
+      <c r="O18" s="60" t="s">
+        <v>368</v>
       </c>
       <c r="P18" s="38">
         <v>1E-3</v>
@@ -3027,28 +3027,28 @@
         <v>10</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G19" s="51" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H19" s="51" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I19" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J19" s="51" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="K19" s="51" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="L19" s="51">
         <v>1</v>
@@ -3060,8 +3060,8 @@
       <c r="N19" s="51">
         <v>100</v>
       </c>
-      <c r="O19" s="73" t="s">
-        <v>376</v>
+      <c r="O19" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P19" s="52">
         <v>4.0000000000000001E-3</v>
@@ -3083,28 +3083,28 @@
         <v>10</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J20" s="37" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="L20" s="37">
         <v>1</v>
@@ -3116,8 +3116,8 @@
       <c r="N20" s="37">
         <v>20</v>
       </c>
-      <c r="O20" s="73" t="s">
-        <v>376</v>
+      <c r="O20" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P20" s="38">
         <v>2.3699999999999999E-2</v>
@@ -3139,28 +3139,28 @@
         <v>10</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H21" s="51" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I21" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J21" s="51" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="L21" s="51">
         <v>1</v>
@@ -3172,8 +3172,8 @@
       <c r="N21" s="51">
         <v>100</v>
       </c>
-      <c r="O21" s="73" t="s">
-        <v>376</v>
+      <c r="O21" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P21" s="52">
         <v>3.8999999999999998E-3</v>
@@ -3195,28 +3195,28 @@
         <v>10</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L22" s="37">
         <v>1</v>
@@ -3228,8 +3228,8 @@
       <c r="N22" s="37">
         <v>10</v>
       </c>
-      <c r="O22" s="70" t="s">
-        <v>376</v>
+      <c r="O22" s="60" t="s">
+        <v>368</v>
       </c>
       <c r="P22" s="38">
         <v>0.2132</v>
@@ -3251,28 +3251,28 @@
         <v>11</v>
       </c>
       <c r="D23" s="51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H23" s="51" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="I23" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J23" s="51" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="K23" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L23" s="51">
         <v>1</v>
@@ -3284,8 +3284,8 @@
       <c r="N23" s="51">
         <v>10</v>
       </c>
-      <c r="O23" s="73" t="s">
-        <v>376</v>
+      <c r="O23" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P23" s="52">
         <v>4.4600000000000001E-2</v>
@@ -3307,28 +3307,28 @@
         <v>11</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J24" s="37" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="K24" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L24" s="37">
         <v>2</v>
@@ -3340,8 +3340,8 @@
       <c r="N24" s="37">
         <v>20</v>
       </c>
-      <c r="O24" s="73" t="s">
-        <v>376</v>
+      <c r="O24" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P24" s="38">
         <v>9.1000000000000004E-3</v>
@@ -3363,28 +3363,28 @@
         <v>12</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G25" s="51" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H25" s="51" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="I25" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J25" s="51" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="K25" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L25" s="51">
         <v>1</v>
@@ -3396,8 +3396,8 @@
       <c r="N25" s="51">
         <v>10</v>
       </c>
-      <c r="O25" s="73" t="s">
-        <v>376</v>
+      <c r="O25" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P25" s="52">
         <v>3.4200000000000001E-2</v>
@@ -3419,28 +3419,28 @@
         <v>11</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J26" s="37" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="K26" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L26" s="37">
         <v>1</v>
@@ -3452,8 +3452,8 @@
       <c r="N26" s="37">
         <v>10</v>
       </c>
-      <c r="O26" s="73" t="s">
-        <v>376</v>
+      <c r="O26" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P26" s="38">
         <v>7.7499999999999999E-2</v>
@@ -3475,28 +3475,28 @@
         <v>11</v>
       </c>
       <c r="D27" s="51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G27" s="51" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H27" s="51" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J27" s="51" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="K27" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L27" s="51">
         <v>1</v>
@@ -3508,8 +3508,8 @@
       <c r="N27" s="51">
         <v>10</v>
       </c>
-      <c r="O27" s="73" t="s">
-        <v>376</v>
+      <c r="O27" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P27" s="52">
         <v>5.4399999999999997E-2</v>
@@ -3531,28 +3531,28 @@
         <v>11</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="K28" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L28" s="37">
         <v>1</v>
@@ -3564,8 +3564,8 @@
       <c r="N28" s="37">
         <v>10</v>
       </c>
-      <c r="O28" s="73" t="s">
-        <v>376</v>
+      <c r="O28" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P28" s="38">
         <v>8.6400000000000005E-2</v>
@@ -3587,28 +3587,28 @@
         <v>11</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G29" s="51" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H29" s="51" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J29" s="51" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="K29" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L29" s="51">
         <v>2</v>
@@ -3620,8 +3620,8 @@
       <c r="N29" s="51">
         <v>20</v>
       </c>
-      <c r="O29" s="73" t="s">
-        <v>376</v>
+      <c r="O29" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P29" s="52">
         <v>3.1699999999999999E-2</v>
@@ -3643,26 +3643,26 @@
         <v>11</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="I30" s="37"/>
       <c r="J30" s="37" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L30" s="37">
         <v>3</v>
@@ -3674,8 +3674,8 @@
       <c r="N30" s="37">
         <v>20</v>
       </c>
-      <c r="O30" s="73" t="s">
-        <v>376</v>
+      <c r="O30" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P30" s="38">
         <v>0.1351</v>
@@ -3697,28 +3697,28 @@
         <v>11</v>
       </c>
       <c r="D31" s="51" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G31" s="51" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H31" s="51" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="I31" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J31" s="51" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="K31" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L31" s="51">
         <v>2</v>
@@ -3730,8 +3730,8 @@
       <c r="N31" s="51">
         <v>20</v>
       </c>
-      <c r="O31" s="73" t="s">
-        <v>376</v>
+      <c r="O31" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P31" s="52">
         <v>4.7500000000000001E-2</v>
@@ -3753,28 +3753,28 @@
         <v>13</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E32" s="37" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J32" s="37" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="K32" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L32" s="37">
         <v>1</v>
@@ -3786,8 +3786,8 @@
       <c r="N32" s="37">
         <v>10</v>
       </c>
-      <c r="O32" s="73" t="s">
-        <v>376</v>
+      <c r="O32" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P32" s="38">
         <v>6.83E-2</v>
@@ -3809,28 +3809,28 @@
         <v>13</v>
       </c>
       <c r="D33" s="51" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F33" s="51" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G33" s="51" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H33" s="51" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="I33" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J33" s="51" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="K33" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L33" s="51">
         <v>1</v>
@@ -3842,8 +3842,8 @@
       <c r="N33" s="51">
         <v>10</v>
       </c>
-      <c r="O33" s="73" t="s">
-        <v>376</v>
+      <c r="O33" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P33" s="52">
         <v>4.5100000000000001E-2</v>
@@ -3865,28 +3865,28 @@
         <v>13</v>
       </c>
       <c r="D34" s="37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E34" s="37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J34" s="37" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="K34" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L34" s="37">
         <v>2</v>
@@ -3898,8 +3898,8 @@
       <c r="N34" s="37">
         <v>20</v>
       </c>
-      <c r="O34" s="73" t="s">
-        <v>376</v>
+      <c r="O34" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P34" s="38">
         <v>5.8999999999999997E-2</v>
@@ -3921,28 +3921,28 @@
         <v>14</v>
       </c>
       <c r="D35" s="51" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F35" s="51" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="G35" s="51" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H35" s="51" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="I35" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J35" s="51" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="K35" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L35" s="51">
         <v>1</v>
@@ -3954,8 +3954,8 @@
       <c r="N35" s="51">
         <v>10</v>
       </c>
-      <c r="O35" s="73" t="s">
-        <v>376</v>
+      <c r="O35" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P35" s="52">
         <v>0.1769</v>
@@ -3977,28 +3977,28 @@
         <v>14</v>
       </c>
       <c r="D36" s="37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E36" s="37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J36" s="37" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="K36" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L36" s="37">
         <v>5</v>
@@ -4010,8 +4010,8 @@
       <c r="N36" s="37">
         <v>30</v>
       </c>
-      <c r="O36" s="73" t="s">
-        <v>376</v>
+      <c r="O36" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P36" s="38">
         <v>0.21840000000000001</v>
@@ -4033,28 +4033,28 @@
         <v>15</v>
       </c>
       <c r="D37" s="51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E37" s="51" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F37" s="51" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="G37" s="51" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H37" s="51" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="I37" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J37" s="51" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="K37" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L37" s="51">
         <v>1</v>
@@ -4066,8 +4066,8 @@
       <c r="N37" s="51">
         <v>10</v>
       </c>
-      <c r="O37" s="73" t="s">
-        <v>376</v>
+      <c r="O37" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P37" s="52">
         <v>0.3211</v>
@@ -4089,28 +4089,28 @@
         <v>15</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J38" s="37" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="K38" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L38" s="37">
         <v>1</v>
@@ -4122,8 +4122,8 @@
       <c r="N38" s="37">
         <v>12</v>
       </c>
-      <c r="O38" s="73" t="s">
-        <v>376</v>
+      <c r="O38" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P38" s="38">
         <v>7.0400000000000004E-2</v>
@@ -4144,86 +4144,82 @@
       <c r="C39" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="D39" s="85" t="s">
-        <v>57</v>
-      </c>
-      <c r="E39" s="85" t="s">
-        <v>120</v>
-      </c>
-      <c r="F39" s="74" t="s">
-        <v>374</v>
-      </c>
-      <c r="G39" s="85" t="s">
-        <v>217</v>
-      </c>
-      <c r="H39" s="74" t="s">
-        <v>373</v>
-      </c>
-      <c r="I39" s="74" t="s">
-        <v>373</v>
-      </c>
-      <c r="J39" s="74" t="s">
-        <v>373</v>
-      </c>
-      <c r="K39" s="85" t="s">
-        <v>373</v>
-      </c>
-      <c r="L39" s="85">
+      <c r="D39" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" s="75" t="s">
+        <v>119</v>
+      </c>
+      <c r="F39" s="64" t="s">
+        <v>366</v>
+      </c>
+      <c r="G39" s="75" t="s">
+        <v>214</v>
+      </c>
+      <c r="H39" s="64" t="s">
+        <v>365</v>
+      </c>
+      <c r="I39" s="64" t="s">
+        <v>365</v>
+      </c>
+      <c r="J39" s="64" t="s">
+        <v>365</v>
+      </c>
+      <c r="K39" s="75" t="s">
+        <v>365</v>
+      </c>
+      <c r="L39" s="75">
         <v>2</v>
       </c>
-      <c r="M39" s="85">
+      <c r="M39" s="75">
         <f t="shared" ref="M39" si="29">L39*5</f>
         <v>10</v>
       </c>
-      <c r="N39" s="85" t="s">
-        <v>373</v>
-      </c>
-      <c r="O39" s="85" t="s">
-        <v>373</v>
-      </c>
-      <c r="P39" s="86" t="s">
-        <v>373</v>
-      </c>
-      <c r="Q39" s="86" t="s">
-        <v>373</v>
-      </c>
-      <c r="R39" s="88" t="s">
-        <v>388</v>
+      <c r="N39" s="75" t="s">
+        <v>365</v>
+      </c>
+      <c r="O39" s="75" t="s">
+        <v>365</v>
+      </c>
+      <c r="P39" s="76" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q39" s="76" t="s">
+        <v>365</v>
+      </c>
+      <c r="R39" s="78" t="s">
+        <v>380</v>
       </c>
       <c r="S39" s="59"/>
     </row>
-    <row r="40" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="46">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
       <c r="C40" s="53" t="s">
-        <v>17</v>
+        <v>388</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>121</v>
+        <v>384</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>218</v>
+        <v>386</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="I40" s="37" t="s">
-        <v>373</v>
-      </c>
-      <c r="J40" s="37" t="s">
-        <v>309</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="I40" s="37"/>
+      <c r="J40" s="37"/>
       <c r="K40" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L40" s="37">
         <v>1</v>
@@ -4232,18 +4228,12 @@
         <f>L40*5</f>
         <v>5</v>
       </c>
-      <c r="N40" s="51">
-        <v>6</v>
-      </c>
-      <c r="O40" s="70" t="s">
-        <v>376</v>
-      </c>
-      <c r="P40" s="52">
-        <v>0.92279999999999995</v>
-      </c>
+      <c r="N40" s="37"/>
+      <c r="O40" s="37"/>
+      <c r="P40" s="38"/>
       <c r="Q40" s="38">
         <f>P40*N40</f>
-        <v>5.5367999999999995</v>
+        <v>0</v>
       </c>
       <c r="R40" s="37"/>
       <c r="S40" s="59"/>
@@ -4255,31 +4245,31 @@
         <v>32</v>
       </c>
       <c r="C41" s="54" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D41" s="51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="G41" s="51" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H41" s="51" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="I41" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J41" s="51" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="K41" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L41" s="51">
         <v>1</v>
@@ -4291,8 +4281,8 @@
       <c r="N41" s="51">
         <v>6</v>
       </c>
-      <c r="O41" s="73" t="s">
-        <v>376</v>
+      <c r="O41" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P41" s="52">
         <v>0.67300000000000004</v>
@@ -4304,61 +4294,61 @@
       <c r="R41" s="51"/>
       <c r="S41" s="59"/>
     </row>
-    <row r="42" spans="1:19" s="84" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="75"/>
-      <c r="B42" s="76">
+    <row r="42" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="65"/>
+      <c r="B42" s="66">
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42" s="78" t="s">
-        <v>60</v>
-      </c>
-      <c r="E42" s="78" t="s">
-        <v>123</v>
-      </c>
-      <c r="F42" s="78" t="s">
-        <v>374</v>
-      </c>
-      <c r="G42" s="78" t="s">
-        <v>174</v>
-      </c>
-      <c r="H42" s="78" t="s">
-        <v>270</v>
-      </c>
-      <c r="I42" s="79" t="s">
-        <v>373</v>
-      </c>
-      <c r="J42" s="79" t="s">
-        <v>373</v>
-      </c>
-      <c r="K42" s="79" t="s">
-        <v>373</v>
-      </c>
-      <c r="L42" s="78">
+      <c r="C42" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="68" t="s">
+        <v>59</v>
+      </c>
+      <c r="E42" s="68" t="s">
+        <v>121</v>
+      </c>
+      <c r="F42" s="68" t="s">
+        <v>366</v>
+      </c>
+      <c r="G42" s="68" t="s">
+        <v>171</v>
+      </c>
+      <c r="H42" s="68" t="s">
+        <v>264</v>
+      </c>
+      <c r="I42" s="69" t="s">
+        <v>365</v>
+      </c>
+      <c r="J42" s="69" t="s">
+        <v>365</v>
+      </c>
+      <c r="K42" s="69" t="s">
+        <v>365</v>
+      </c>
+      <c r="L42" s="68">
         <v>1</v>
       </c>
-      <c r="M42" s="78">
+      <c r="M42" s="68">
         <f>L42*5</f>
         <v>5</v>
       </c>
-      <c r="N42" s="78">
+      <c r="N42" s="68">
         <v>6</v>
       </c>
-      <c r="O42" s="80" t="s">
-        <v>385</v>
-      </c>
-      <c r="P42" s="81">
+      <c r="O42" s="70" t="s">
+        <v>377</v>
+      </c>
+      <c r="P42" s="71">
         <v>1.01</v>
       </c>
-      <c r="Q42" s="82">
+      <c r="Q42" s="72">
         <f>P42*N42</f>
         <v>6.0600000000000005</v>
       </c>
-      <c r="R42" s="78"/>
-      <c r="S42" s="83"/>
+      <c r="R42" s="68"/>
+      <c r="S42" s="73"/>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
@@ -4366,32 +4356,30 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="53" t="s">
-        <v>20</v>
+      <c r="C43" s="54" t="s">
+        <v>19</v>
       </c>
       <c r="D43" s="51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E43" s="51" t="s">
-        <v>124</v>
-      </c>
-      <c r="F43" s="37" t="s">
-        <v>374</v>
+        <v>381</v>
+      </c>
+      <c r="F43" s="51" t="s">
+        <v>382</v>
       </c>
       <c r="G43" s="51" t="s">
-        <v>219</v>
+        <v>382</v>
       </c>
       <c r="H43" s="51" t="s">
-        <v>271</v>
-      </c>
-      <c r="I43" s="51" t="s">
-        <v>373</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="I43" s="51"/>
       <c r="J43" s="51" t="s">
-        <v>311</v>
+        <v>383</v>
       </c>
       <c r="K43" s="51" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="L43" s="51">
         <v>1</v>
@@ -4400,18 +4388,12 @@
         <f t="shared" ref="M43" si="32">L43*5</f>
         <v>5</v>
       </c>
-      <c r="N43" s="51">
-        <v>6</v>
-      </c>
-      <c r="O43" s="73" t="s">
-        <v>376</v>
-      </c>
-      <c r="P43" s="52">
-        <v>0.49009999999999998</v>
-      </c>
+      <c r="N43" s="51"/>
+      <c r="O43" s="51"/>
+      <c r="P43" s="52"/>
       <c r="Q43" s="52">
         <f t="shared" ref="Q43" si="33">P43*N43</f>
-        <v>2.9405999999999999</v>
+        <v>0</v>
       </c>
       <c r="R43" s="51"/>
       <c r="S43" s="59"/>
@@ -4423,31 +4405,31 @@
         <v>35</v>
       </c>
       <c r="C44" s="53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D44" s="37" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E44" s="37" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J44" s="37" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="K44" s="37" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="L44" s="37">
         <v>1</v>
@@ -4459,8 +4441,8 @@
       <c r="N44" s="37">
         <v>10</v>
       </c>
-      <c r="O44" s="73" t="s">
-        <v>376</v>
+      <c r="O44" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P44" s="38">
         <v>8.5300000000000001E-2</v>
@@ -4479,31 +4461,31 @@
         <v>36</v>
       </c>
       <c r="C45" s="53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D45" s="51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E45" s="51" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F45" s="51" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G45" s="51" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="H45" s="51" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="I45" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J45" s="51" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="K45" s="51" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="L45" s="51">
         <v>1</v>
@@ -4515,8 +4497,8 @@
       <c r="N45" s="51">
         <v>50</v>
       </c>
-      <c r="O45" s="73" t="s">
-        <v>376</v>
+      <c r="O45" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P45" s="52">
         <v>8.3000000000000001E-3</v>
@@ -4535,31 +4517,31 @@
         <v>37</v>
       </c>
       <c r="C46" s="53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L46" s="37">
         <v>3</v>
@@ -4571,8 +4553,8 @@
       <c r="N46" s="51">
         <v>20</v>
       </c>
-      <c r="O46" s="73" t="s">
-        <v>376</v>
+      <c r="O46" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P46" s="52">
         <v>5.1499999999999997E-2</v>
@@ -4591,31 +4573,31 @@
         <v>38</v>
       </c>
       <c r="C47" s="54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D47" s="51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E47" s="51" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F47" s="51" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G47" s="51" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H47" s="51" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="I47" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J47" s="51" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="K47" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L47" s="51">
         <v>1</v>
@@ -4627,8 +4609,8 @@
       <c r="N47" s="51">
         <v>20</v>
       </c>
-      <c r="O47" s="73" t="s">
-        <v>376</v>
+      <c r="O47" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P47" s="52">
         <v>3.1300000000000001E-2</v>
@@ -4647,51 +4629,51 @@
         <v>39</v>
       </c>
       <c r="C48" s="53" t="s">
-        <v>386</v>
-      </c>
-      <c r="D48" s="74" t="s">
-        <v>66</v>
-      </c>
-      <c r="E48" s="74" t="s">
-        <v>129</v>
-      </c>
-      <c r="F48" s="74" t="s">
-        <v>374</v>
-      </c>
-      <c r="G48" s="74" t="s">
-        <v>177</v>
-      </c>
-      <c r="H48" s="74" t="s">
-        <v>373</v>
-      </c>
-      <c r="I48" s="74" t="s">
-        <v>373</v>
-      </c>
-      <c r="J48" s="74" t="s">
-        <v>373</v>
-      </c>
-      <c r="K48" s="74" t="s">
-        <v>373</v>
-      </c>
-      <c r="L48" s="74">
+        <v>378</v>
+      </c>
+      <c r="D48" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="E48" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="F48" s="64" t="s">
+        <v>366</v>
+      </c>
+      <c r="G48" s="64" t="s">
+        <v>174</v>
+      </c>
+      <c r="H48" s="64" t="s">
+        <v>365</v>
+      </c>
+      <c r="I48" s="64" t="s">
+        <v>365</v>
+      </c>
+      <c r="J48" s="64" t="s">
+        <v>365</v>
+      </c>
+      <c r="K48" s="64" t="s">
+        <v>365</v>
+      </c>
+      <c r="L48" s="64">
         <v>4</v>
       </c>
-      <c r="M48" s="74">
+      <c r="M48" s="64">
         <f>L48*5</f>
         <v>20</v>
       </c>
-      <c r="N48" s="74"/>
-      <c r="O48" s="85" t="s">
-        <v>373</v>
-      </c>
-      <c r="P48" s="87" t="s">
-        <v>373</v>
-      </c>
-      <c r="Q48" s="87" t="s">
-        <v>373</v>
-      </c>
-      <c r="R48" s="88" t="s">
-        <v>388</v>
+      <c r="N48" s="64"/>
+      <c r="O48" s="75" t="s">
+        <v>365</v>
+      </c>
+      <c r="P48" s="77" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q48" s="77" t="s">
+        <v>365</v>
+      </c>
+      <c r="R48" s="78" t="s">
+        <v>380</v>
       </c>
       <c r="S48" s="59"/>
     </row>
@@ -4702,31 +4684,31 @@
         <v>40</v>
       </c>
       <c r="C49" s="54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D49" s="51" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E49" s="51" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F49" s="51" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G49" s="51" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H49" s="51" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="I49" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J49" s="51" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="K49" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L49" s="51">
         <v>6</v>
@@ -4738,8 +4720,8 @@
       <c r="N49" s="51">
         <v>40</v>
       </c>
-      <c r="O49" s="73" t="s">
-        <v>376</v>
+      <c r="O49" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P49" s="52">
         <v>2.1899999999999999E-2</v>
@@ -4758,31 +4740,31 @@
         <v>41</v>
       </c>
       <c r="C50" s="53" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D50" s="37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E50" s="37" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F50" s="37" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G50" s="37" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H50" s="37" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="I50" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J50" s="37" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="K50" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L50" s="37">
         <v>1</v>
@@ -4794,8 +4776,8 @@
       <c r="N50" s="37">
         <v>10</v>
       </c>
-      <c r="O50" s="73" t="s">
-        <v>376</v>
+      <c r="O50" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P50" s="38">
         <v>3.1099999999999999E-2</v>
@@ -4814,31 +4796,31 @@
         <v>42</v>
       </c>
       <c r="C51" s="54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D51" s="51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E51" s="51" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F51" s="51" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G51" s="51" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H51" s="51" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I51" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J51" s="51" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="K51" s="51" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="L51" s="51">
         <v>1</v>
@@ -4850,8 +4832,8 @@
       <c r="N51" s="51">
         <v>100</v>
       </c>
-      <c r="O51" s="73" t="s">
-        <v>376</v>
+      <c r="O51" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P51" s="52">
         <v>6.9999999999999999E-4</v>
@@ -4870,31 +4852,31 @@
         <v>43</v>
       </c>
       <c r="C52" s="54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D52" s="37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E52" s="37" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F52" s="37" t="s">
-        <v>180</v>
-      </c>
-      <c r="G52" s="74" t="s">
-        <v>227</v>
+        <v>177</v>
+      </c>
+      <c r="G52" s="64" t="s">
+        <v>222</v>
       </c>
       <c r="H52" s="51" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I52" s="51" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="J52" s="51" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="K52" s="51" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="L52" s="37">
         <v>2</v>
@@ -4906,8 +4888,8 @@
       <c r="N52" s="51">
         <v>100</v>
       </c>
-      <c r="O52" s="73" t="s">
-        <v>376</v>
+      <c r="O52" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P52" s="52">
         <v>5.0000000000000001E-4</v>
@@ -4926,31 +4908,31 @@
         <v>44</v>
       </c>
       <c r="C53" s="54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D53" s="51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E53" s="51" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F53" s="51" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G53" s="51" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="H53" s="51" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I53" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J53" s="51" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="K53" s="51" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="L53" s="51">
         <v>6</v>
@@ -4962,8 +4944,8 @@
       <c r="N53" s="51">
         <v>100</v>
       </c>
-      <c r="O53" s="73" t="s">
-        <v>376</v>
+      <c r="O53" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P53" s="52">
         <v>8.9999999999999998E-4</v>
@@ -4982,31 +4964,31 @@
         <v>45</v>
       </c>
       <c r="C54" s="54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D54" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E54" s="37" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F54" s="37" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G54" s="37" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="H54" s="37" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I54" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J54" s="37" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="K54" s="37" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="L54" s="37">
         <v>1</v>
@@ -5018,8 +5000,8 @@
       <c r="N54" s="37">
         <v>100</v>
       </c>
-      <c r="O54" s="73" t="s">
-        <v>376</v>
+      <c r="O54" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P54" s="38">
         <v>5.9999999999999995E-4</v>
@@ -5038,31 +5020,31 @@
         <v>46</v>
       </c>
       <c r="C55" s="54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D55" s="51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E55" s="51" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F55" s="51" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G55" s="51" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H55" s="51" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I55" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J55" s="51" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="K55" s="51" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="L55" s="51">
         <v>17</v>
@@ -5074,8 +5056,8 @@
       <c r="N55" s="51">
         <v>100</v>
       </c>
-      <c r="O55" s="73" t="s">
-        <v>376</v>
+      <c r="O55" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P55" s="52">
         <v>6.9999999999999999E-4</v>
@@ -5094,31 +5076,31 @@
         <v>47</v>
       </c>
       <c r="C56" s="54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D56" s="37" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E56" s="37" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F56" s="37" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="H56" s="37" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I56" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J56" s="37" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="K56" s="37" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="L56" s="37">
         <v>3</v>
@@ -5130,8 +5112,8 @@
       <c r="N56" s="37">
         <v>100</v>
       </c>
-      <c r="O56" s="73" t="s">
-        <v>376</v>
+      <c r="O56" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P56" s="38">
         <v>6.9999999999999999E-4</v>
@@ -5150,31 +5132,31 @@
         <v>48</v>
       </c>
       <c r="C57" s="54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D57" s="51" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E57" s="51" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F57" s="51" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G57" s="51" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="H57" s="51" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I57" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J57" s="51" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="K57" s="51" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="L57" s="51">
         <v>1</v>
@@ -5186,8 +5168,8 @@
       <c r="N57" s="51">
         <v>100</v>
       </c>
-      <c r="O57" s="73" t="s">
-        <v>376</v>
+      <c r="O57" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P57" s="52">
         <v>5.9999999999999995E-4</v>
@@ -5206,31 +5188,31 @@
         <v>49</v>
       </c>
       <c r="C58" s="53" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D58" s="37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E58" s="37" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F58" s="37" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="H58" s="37" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I58" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J58" s="37" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="K58" s="37" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="L58" s="37">
         <v>5</v>
@@ -5242,8 +5224,8 @@
       <c r="N58" s="37">
         <v>100</v>
       </c>
-      <c r="O58" s="73" t="s">
-        <v>376</v>
+      <c r="O58" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P58" s="38">
         <v>6.9999999999999999E-4</v>
@@ -5262,31 +5244,31 @@
         <v>50</v>
       </c>
       <c r="C59" s="53" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D59" s="51" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E59" s="51" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F59" s="51" t="s">
-        <v>179</v>
-      </c>
-      <c r="G59" s="74" t="s">
-        <v>234</v>
+        <v>176</v>
+      </c>
+      <c r="G59" s="64" t="s">
+        <v>229</v>
       </c>
       <c r="H59" s="51" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="I59" s="51" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="J59" s="51" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="K59" s="51" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="L59" s="51">
         <v>4</v>
@@ -5298,8 +5280,8 @@
       <c r="N59" s="51">
         <v>100</v>
       </c>
-      <c r="O59" s="73" t="s">
-        <v>376</v>
+      <c r="O59" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P59" s="52">
         <v>4.0000000000000002E-4</v>
@@ -5318,31 +5300,31 @@
         <v>51</v>
       </c>
       <c r="C60" s="53" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D60" s="37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E60" s="37" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F60" s="37" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G60" s="37" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="H60" s="37" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I60" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J60" s="37" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="K60" s="37" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="L60" s="37">
         <v>2</v>
@@ -5354,8 +5336,8 @@
       <c r="N60" s="37">
         <v>100</v>
       </c>
-      <c r="O60" s="73" t="s">
-        <v>376</v>
+      <c r="O60" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P60" s="38">
         <v>1.2999999999999999E-3</v>
@@ -5374,31 +5356,31 @@
         <v>52</v>
       </c>
       <c r="C61" s="54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D61" s="51" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E61" s="51" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F61" s="51" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="G61" s="51" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="H61" s="51" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="I61" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J61" s="51" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="K61" s="51" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="L61" s="51">
         <v>2</v>
@@ -5410,8 +5392,8 @@
       <c r="N61" s="51">
         <v>100</v>
       </c>
-      <c r="O61" s="73" t="s">
-        <v>376</v>
+      <c r="O61" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P61" s="52">
         <v>6.8999999999999999E-3</v>
@@ -5430,31 +5412,31 @@
         <v>53</v>
       </c>
       <c r="C62" s="53" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D62" s="37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E62" s="37" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F62" s="37" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="G62" s="37" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H62" s="37" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="I62" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J62" s="37" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="K62" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L62" s="37">
         <v>1</v>
@@ -5466,8 +5448,8 @@
       <c r="N62" s="37">
         <v>10</v>
       </c>
-      <c r="O62" s="73" t="s">
-        <v>376</v>
+      <c r="O62" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P62" s="38">
         <v>0.12659999999999999</v>
@@ -5486,31 +5468,31 @@
         <v>54</v>
       </c>
       <c r="C63" s="54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D63" s="51" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E63" s="51" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F63" s="51" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G63" s="51" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H63" s="51" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="I63" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J63" s="51" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="K63" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L63" s="51">
         <v>1</v>
@@ -5522,8 +5504,8 @@
       <c r="N63" s="51">
         <v>6</v>
       </c>
-      <c r="O63" s="73" t="s">
-        <v>376</v>
+      <c r="O63" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P63" s="52">
         <v>0.35320000000000001</v>
@@ -5542,31 +5524,31 @@
         <v>55</v>
       </c>
       <c r="C64" s="53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D64" s="37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E64" s="37" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F64" s="37" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G64" s="37" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="H64" s="37" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="I64" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J64" s="37" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="K64" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L64" s="37">
         <v>1</v>
@@ -5578,8 +5560,8 @@
       <c r="N64" s="37">
         <v>6</v>
       </c>
-      <c r="O64" s="73" t="s">
-        <v>376</v>
+      <c r="O64" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P64" s="38">
         <v>0.46460000000000001</v>
@@ -5598,31 +5580,31 @@
         <v>56</v>
       </c>
       <c r="C65" s="54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D65" s="51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E65" s="51" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F65" s="51" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G65" s="51" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="H65" s="51" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="I65" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J65" s="51" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="K65" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L65" s="51">
         <v>1</v>
@@ -5634,8 +5616,8 @@
       <c r="N65" s="51">
         <v>6</v>
       </c>
-      <c r="O65" s="73" t="s">
-        <v>376</v>
+      <c r="O65" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P65" s="52">
         <v>0.37230000000000002</v>
@@ -5654,31 +5636,31 @@
         <v>57</v>
       </c>
       <c r="C66" s="53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D66" s="37" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E66" s="37" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F66" s="37" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G66" s="37" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H66" s="37" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="I66" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J66" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="K66" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L66" s="37">
         <v>1</v>
@@ -5690,8 +5672,8 @@
       <c r="N66" s="37">
         <v>6</v>
       </c>
-      <c r="O66" s="73" t="s">
-        <v>375</v>
+      <c r="O66" s="63" t="s">
+        <v>367</v>
       </c>
       <c r="P66" s="38">
         <v>2.5099999999999998</v>
@@ -5710,29 +5692,29 @@
         <v>58</v>
       </c>
       <c r="C67" s="54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D67" s="51" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E67" s="51" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F67" s="51" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G67" s="51" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="H67" s="51" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="I67" s="51"/>
       <c r="J67" s="51" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="K67" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L67" s="51">
         <v>1</v>
@@ -5744,8 +5726,8 @@
       <c r="N67" s="51">
         <v>6</v>
       </c>
-      <c r="O67" s="73" t="s">
-        <v>376</v>
+      <c r="O67" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P67" s="52">
         <v>1.8821000000000001</v>
@@ -5764,31 +5746,31 @@
         <v>59</v>
       </c>
       <c r="C68" s="53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D68" s="37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E68" s="37" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F68" s="37" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="G68" s="37" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H68" s="37" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="I68" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J68" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="K68" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L68" s="37">
         <v>1</v>
@@ -5800,8 +5782,8 @@
       <c r="N68" s="51">
         <v>6</v>
       </c>
-      <c r="O68" s="70" t="s">
-        <v>377</v>
+      <c r="O68" s="60" t="s">
+        <v>369</v>
       </c>
       <c r="P68" s="52">
         <v>27.036000000000001</v>
@@ -5823,28 +5805,28 @@
         <v>12</v>
       </c>
       <c r="D69" s="51" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E69" s="51" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F69" s="51" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G69" s="51" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="H69" s="51" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="I69" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J69" s="51" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="K69" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L69" s="51">
         <v>1</v>
@@ -5856,8 +5838,8 @@
       <c r="N69" s="37">
         <v>20</v>
       </c>
-      <c r="O69" s="70" t="s">
-        <v>376</v>
+      <c r="O69" s="60" t="s">
+        <v>368</v>
       </c>
       <c r="P69" s="38">
         <v>3.85E-2</v>
@@ -5876,31 +5858,31 @@
         <v>61</v>
       </c>
       <c r="C70" s="53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D70" s="37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E70" s="37" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F70" s="37" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G70" s="37" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="H70" s="37" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="I70" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J70" s="37" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="K70" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L70" s="37">
         <v>1</v>
@@ -5912,8 +5894,8 @@
       <c r="N70" s="51">
         <v>6</v>
       </c>
-      <c r="O70" s="70" t="s">
-        <v>376</v>
+      <c r="O70" s="60" t="s">
+        <v>368</v>
       </c>
       <c r="P70" s="52">
         <v>0.43280000000000002</v>
@@ -5932,31 +5914,31 @@
         <v>62</v>
       </c>
       <c r="C71" s="54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D71" s="51" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E71" s="51" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F71" s="51" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G71" s="51" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="H71" s="51" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="I71" s="51" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J71" s="51" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="K71" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="L71" s="51">
         <v>1</v>
@@ -5968,8 +5950,8 @@
       <c r="N71" s="51">
         <v>6</v>
       </c>
-      <c r="O71" s="73" t="s">
-        <v>376</v>
+      <c r="O71" s="63" t="s">
+        <v>368</v>
       </c>
       <c r="P71" s="52">
         <v>0.80659999999999998</v>
@@ -5988,31 +5970,31 @@
         <v>63</v>
       </c>
       <c r="C72" s="53" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D72" s="37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E72" s="37" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F72" s="37" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="G72" s="37" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H72" s="37" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="I72" s="37" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J72" s="37" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="K72" s="37" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="L72" s="37">
         <v>1</v>
@@ -6024,8 +6006,8 @@
       <c r="N72" s="37">
         <v>10</v>
       </c>
-      <c r="O72" s="70" t="s">
-        <v>376</v>
+      <c r="O72" s="60" t="s">
+        <v>368</v>
       </c>
       <c r="P72" s="38">
         <v>0.08</v>
@@ -6051,17 +6033,17 @@
       <c r="K73" s="45"/>
       <c r="L73" s="45"/>
       <c r="M73" s="45"/>
-      <c r="N73" s="68" t="s">
+      <c r="N73" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="O73" s="69"/>
-      <c r="P73" s="69"/>
+      <c r="O73" s="88"/>
+      <c r="P73" s="88"/>
       <c r="Q73" s="48">
         <f>SUM(Q10:Q72)</f>
-        <v>277.12860000000001</v>
-      </c>
-      <c r="R73" s="64"/>
-      <c r="S73" s="65"/>
+        <v>268.65120000000002</v>
+      </c>
+      <c r="R73" s="83"/>
+      <c r="S73" s="84"/>
     </row>
     <row r="74" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
@@ -6077,17 +6059,17 @@
       <c r="K74" s="10"/>
       <c r="L74" s="10"/>
       <c r="M74" s="10"/>
-      <c r="N74" s="68" t="s">
+      <c r="N74" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="O74" s="69"/>
-      <c r="P74" s="69"/>
+      <c r="O74" s="88"/>
+      <c r="P74" s="88"/>
       <c r="Q74" s="49">
         <f>Q73/5</f>
-        <v>55.425719999999998</v>
-      </c>
-      <c r="R74" s="66"/>
-      <c r="S74" s="67"/>
+        <v>53.730240000000002</v>
+      </c>
+      <c r="R74" s="85"/>
+      <c r="S74" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6100,7 +6082,7 @@
   <hyperlinks>
     <hyperlink ref="O18" r:id="rId1"/>
     <hyperlink ref="O22" r:id="rId2"/>
-    <hyperlink ref="O40" r:id="rId3"/>
+    <hyperlink ref="O40" r:id="rId3" display="LCSC"/>
     <hyperlink ref="O68" r:id="rId4"/>
     <hyperlink ref="O69" r:id="rId5"/>
     <hyperlink ref="O70" r:id="rId6"/>
@@ -6140,7 +6122,7 @@
     <hyperlink ref="O33" r:id="rId40"/>
     <hyperlink ref="O35" r:id="rId41"/>
     <hyperlink ref="O41" r:id="rId42"/>
-    <hyperlink ref="O43" r:id="rId43"/>
+    <hyperlink ref="O43" r:id="rId43" display="LCSC"/>
     <hyperlink ref="O44" r:id="rId44"/>
     <hyperlink ref="O47" r:id="rId45"/>
     <hyperlink ref="O57" r:id="rId46"/>

--- a/Design Files/LightSPT-Device-v1.0/BOM/eSpark_BOM_Light_spt_device.xlsx
+++ b/Design Files/LightSPT-Device-v1.0/BOM/eSpark_BOM_Light_spt_device.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="411">
   <si>
     <t>Component list</t>
   </si>
@@ -111,9 +111,6 @@
     <t>C1, C3, C7, C9, C12, C17, C18, C19, C22, C23, C25, C32, C37, C38, C39, C40, C41, C42, C43, C44, C45, C46, C47</t>
   </si>
   <si>
-    <t>C2, C8, C20</t>
-  </si>
-  <si>
     <t>C4</t>
   </si>
   <si>
@@ -123,9 +120,6 @@
     <t>C13, C16, C21, C24, C33</t>
   </si>
   <si>
-    <t>C14, C15</t>
-  </si>
-  <si>
     <t>C26, C27, C34, C35, C36</t>
   </si>
   <si>
@@ -372,9 +366,6 @@
     <t>1x3P 18A -40℃~+105℃ 250V Black 12~30 Straight pin 5.08mm 2.5 1 3 Plugin,P=5.08mm Screw terminal ROHS</t>
   </si>
   <si>
-    <t>CONN HEADER SMD 11POS 1.25MM</t>
-  </si>
-  <si>
     <t>1x6P SH 1 1mm 6 SMD,P=1mm Wire To Board / Wire To Wire Connector ROHS</t>
   </si>
   <si>
@@ -657,9 +648,6 @@
     <t>SMD0805P020TF</t>
   </si>
   <si>
-    <t>53398-1171</t>
-  </si>
-  <si>
     <t>C145963</t>
   </si>
   <si>
@@ -804,9 +792,6 @@
     <t>DIBO</t>
   </si>
   <si>
-    <t>Molex</t>
-  </si>
-  <si>
     <t>BOOMELE</t>
   </si>
   <si>
@@ -1149,9 +1134,6 @@
     <t>C25152</t>
   </si>
   <si>
-    <t>C504827</t>
-  </si>
-  <si>
     <t>Chipsmall</t>
   </si>
   <si>
@@ -1186,6 +1168,90 @@
   </si>
   <si>
     <t>SMA Connector</t>
+  </si>
+  <si>
+    <t>C2, C8, C15, C20</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>C48</t>
+  </si>
+  <si>
+    <t>C49</t>
+  </si>
+  <si>
+    <t>L4</t>
+  </si>
+  <si>
+    <t>CC0201CRNPO9BN2R7</t>
+  </si>
+  <si>
+    <t>CC0201BRNPO9BN4R7</t>
+  </si>
+  <si>
+    <t>F0503-ZV-18-20T-R</t>
+  </si>
+  <si>
+    <t>FHW0603UC1N6KST</t>
+  </si>
+  <si>
+    <t>CAP CER 2.7PF 50V C0G/NPO 0201</t>
+  </si>
+  <si>
+    <t>CAP-0201</t>
+  </si>
+  <si>
+    <t>C325439</t>
+  </si>
+  <si>
+    <t>2.7pF</t>
+  </si>
+  <si>
+    <t>CAP CER 4.7PF 50V C0G/NPO 0201</t>
+  </si>
+  <si>
+    <t>C505471</t>
+  </si>
+  <si>
+    <t>4.7pF</t>
+  </si>
+  <si>
+    <t>Slide Lock 18P Contact, Vertical - One Side Brick nogging 0.5mm SMD,P=0.5mm FFC/FPC Connectors ROHS</t>
+  </si>
+  <si>
+    <t>XFCN</t>
+  </si>
+  <si>
+    <t>C481243</t>
+  </si>
+  <si>
+    <t>700mA 1.6nH ±10% 40mΩ 0603 Inductors (SMD) ROHS</t>
+  </si>
+  <si>
+    <t>FH</t>
+  </si>
+  <si>
+    <t>C317978</t>
+  </si>
+  <si>
+    <t>1.6nH</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>1.8 3dBi Vertical 50W - Antennas ROHS</t>
+  </si>
+  <si>
+    <t>BWGSMJWX105-7KJ</t>
+  </si>
+  <si>
+    <t>BAT WIRELESS</t>
+  </si>
+  <si>
+    <t>C497021</t>
   </si>
 </sst>
 </file>
@@ -1666,7 +1732,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1911,6 +1977,9 @@
     <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2254,7 +2323,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S74"/>
+  <dimension ref="A1:Z78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -2275,9 +2344,12 @@
     <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -2298,7 +2370,7 @@
       <c r="R1" s="79"/>
       <c r="S1" s="80"/>
     </row>
-    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="21"/>
       <c r="C2" s="31"/>
@@ -2307,7 +2379,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2323,7 +2395,7 @@
       <c r="R2" s="4"/>
       <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="22"/>
       <c r="C3" s="32"/>
@@ -2332,7 +2404,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2348,7 +2420,7 @@
       <c r="R3" s="5"/>
       <c r="S3" s="81"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="22"/>
       <c r="C4" s="32"/>
@@ -2357,7 +2429,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2373,7 +2445,7 @@
       <c r="R4" s="6"/>
       <c r="S4" s="82"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="22"/>
       <c r="C5" s="32"/>
@@ -2398,7 +2470,7 @@
       <c r="R5" s="6"/>
       <c r="S5" s="82"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="23"/>
       <c r="C6" s="33"/>
@@ -2419,7 +2491,7 @@
       <c r="R6" s="6"/>
       <c r="S6" s="82"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="24"/>
       <c r="C7" s="34"/>
@@ -2440,7 +2512,7 @@
       <c r="R7" s="8"/>
       <c r="S7" s="82"/>
     </row>
-    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="27"/>
       <c r="C8" s="35"/>
@@ -2461,7 +2533,7 @@
       <c r="R8" s="8"/>
       <c r="S8" s="82"/>
     </row>
-    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="30" t="s">
         <v>4</v>
@@ -2473,52 +2545,52 @@
         <v>26</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>351</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>352</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>348</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>353</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>354</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>355</v>
+      </c>
+      <c r="P9" s="30" t="s">
         <v>356</v>
       </c>
-      <c r="J9" s="30" t="s">
-        <v>278</v>
-      </c>
-      <c r="K9" s="30" t="s">
+      <c r="Q9" s="30" t="s">
         <v>357</v>
       </c>
-      <c r="L9" s="30" t="s">
-        <v>353</v>
-      </c>
-      <c r="M9" s="30" t="s">
+      <c r="R9" s="30" t="s">
         <v>358</v>
       </c>
-      <c r="N9" s="30" t="s">
+      <c r="S9" s="30" t="s">
         <v>359</v>
       </c>
-      <c r="O9" s="30" t="s">
-        <v>360</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>361</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>362</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>363</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -2532,22 +2604,22 @@
       </c>
       <c r="E10" s="64"/>
       <c r="F10" s="64" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="G10" s="64" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H10" s="64" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="I10" s="64" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J10" s="64" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="K10" s="64" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="L10" s="64">
         <v>1</v>
@@ -2557,24 +2629,24 @@
         <v>5</v>
       </c>
       <c r="N10" s="64" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="O10" s="64" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="P10" s="77" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="Q10" s="77" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="R10" s="64"/>
       <c r="S10" s="50"/>
     </row>
-    <row r="11" spans="1:19" s="62" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" s="62" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="61"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B71" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B74" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
@@ -2584,25 +2656,25 @@
         <v>28</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="I11" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J11" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="K11" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
@@ -2615,7 +2687,7 @@
         <v>6</v>
       </c>
       <c r="O11" s="60" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="P11" s="38">
         <v>1.59</v>
@@ -2626,8 +2698,14 @@
       </c>
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
-    </row>
-    <row r="12" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+      <c r="U11"/>
+      <c r="V11"/>
+      <c r="W11"/>
+      <c r="X11"/>
+      <c r="Y11"/>
+      <c r="Z11"/>
+    </row>
+    <row r="12" spans="1:26" ht="48" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="46">
         <f>ROW(B12) - ROW($B$9)</f>
@@ -2640,25 +2718,25 @@
         <v>29</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="L12" s="37">
         <v>23</v>
@@ -2671,7 +2749,7 @@
         <v>150</v>
       </c>
       <c r="O12" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P12" s="38">
         <v>1.0500000000000001E-2</v>
@@ -2683,7 +2761,7 @@
       <c r="R12" s="37"/>
       <c r="S12" s="59"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="47">
         <f t="shared" si="0"/>
@@ -2692,42 +2770,42 @@
       <c r="C13" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="51" t="s">
-        <v>30</v>
+      <c r="D13" s="37" t="s">
+        <v>383</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I13" s="51" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="L13" s="51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M13" s="51">
         <f t="shared" ref="M13" si="3">L13*5</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N13" s="51">
         <v>50</v>
       </c>
       <c r="O13" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P13" s="52">
         <v>1.0800000000000001E-2</v>
@@ -2739,7 +2817,7 @@
       <c r="R13" s="51"/>
       <c r="S13" s="59"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="46">
         <f>ROW(B14) - ROW($B$9)</f>
@@ -2749,28 +2827,28 @@
         <v>10</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="L14" s="37">
         <v>1</v>
@@ -2783,7 +2861,7 @@
         <v>100</v>
       </c>
       <c r="O14" s="60" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P14" s="38">
         <v>2.2000000000000001E-3</v>
@@ -2795,7 +2873,7 @@
       <c r="R14" s="37"/>
       <c r="S14" s="59"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="47">
         <f t="shared" si="0"/>
@@ -2805,26 +2883,26 @@
         <v>10</v>
       </c>
       <c r="D15" s="51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G15" s="51" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H15" s="51" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="I15" s="51"/>
       <c r="J15" s="51" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="L15" s="51">
         <v>4</v>
@@ -2837,7 +2915,7 @@
         <v>21</v>
       </c>
       <c r="O15" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P15" s="52">
         <v>0.39779999999999999</v>
@@ -2849,7 +2927,7 @@
       <c r="R15" s="51"/>
       <c r="S15" s="59"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="46">
         <f>ROW(B16) - ROW($B$9)</f>
@@ -2859,28 +2937,28 @@
         <v>10</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G16" s="64" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="L16" s="37">
         <v>5</v>
@@ -2893,7 +2971,7 @@
         <v>30</v>
       </c>
       <c r="O16" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P16" s="38">
         <v>3.7199999999999997E-2</v>
@@ -2915,41 +2993,41 @@
         <v>10</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>34</v>
+        <v>384</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H17" s="51" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="I17" s="51" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J17" s="51" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="L17" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M17" s="51">
         <f t="shared" ref="M17" si="7">L17*5</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N17" s="51">
         <v>100</v>
       </c>
       <c r="O17" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P17" s="52">
         <v>8.9999999999999998E-4</v>
@@ -2971,28 +3049,28 @@
         <v>10</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="K18" s="37" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L18" s="37">
         <v>5</v>
@@ -3005,7 +3083,7 @@
         <v>100</v>
       </c>
       <c r="O18" s="60" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P18" s="38">
         <v>1E-3</v>
@@ -3027,28 +3105,28 @@
         <v>10</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G19" s="51" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H19" s="51" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="I19" s="51" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J19" s="51" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="K19" s="51" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="L19" s="51">
         <v>1</v>
@@ -3061,7 +3139,7 @@
         <v>100</v>
       </c>
       <c r="O19" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P19" s="52">
         <v>4.0000000000000001E-3</v>
@@ -3083,28 +3161,28 @@
         <v>10</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J20" s="37" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="L20" s="37">
         <v>1</v>
@@ -3117,7 +3195,7 @@
         <v>20</v>
       </c>
       <c r="O20" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P20" s="38">
         <v>2.3699999999999999E-2</v>
@@ -3139,28 +3217,28 @@
         <v>10</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H21" s="51" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="I21" s="51" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J21" s="51" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="L21" s="51">
         <v>1</v>
@@ -3173,7 +3251,7 @@
         <v>100</v>
       </c>
       <c r="O21" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P21" s="52">
         <v>3.8999999999999998E-3</v>
@@ -3195,28 +3273,28 @@
         <v>10</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="L22" s="37">
         <v>1</v>
@@ -3229,7 +3307,7 @@
         <v>10</v>
       </c>
       <c r="O22" s="60" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P22" s="38">
         <v>0.2132</v>
@@ -3241,116 +3319,116 @@
       <c r="R22" s="37"/>
       <c r="S22" s="59"/>
     </row>
-    <row r="23" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="47">
-        <f t="shared" si="0"/>
+      <c r="B23" s="46">
+        <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
-      <c r="C23" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="51" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="F23" s="51" t="s">
-        <v>158</v>
-      </c>
-      <c r="G23" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="H23" s="51" t="s">
-        <v>248</v>
-      </c>
-      <c r="I23" s="51" t="s">
-        <v>365</v>
-      </c>
-      <c r="J23" s="51" t="s">
-        <v>289</v>
+      <c r="C23" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="37" t="s">
+        <v>385</v>
+      </c>
+      <c r="E23" s="37" t="s">
+        <v>392</v>
+      </c>
+      <c r="F23" s="37" t="s">
+        <v>393</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>388</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="I23" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="J23" s="37" t="s">
+        <v>394</v>
       </c>
       <c r="K23" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="L23" s="51">
+        <v>395</v>
+      </c>
+      <c r="L23" s="37">
         <v>1</v>
       </c>
-      <c r="M23" s="51">
-        <f t="shared" ref="M23" si="13">L23*5</f>
+      <c r="M23" s="37">
+        <f>L23*5</f>
         <v>5</v>
       </c>
-      <c r="N23" s="51">
-        <v>10</v>
-      </c>
-      <c r="O23" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P23" s="52">
-        <v>4.4600000000000001E-2</v>
-      </c>
-      <c r="Q23" s="52">
-        <f t="shared" ref="Q23" si="14">P23*N23</f>
-        <v>0.44600000000000001</v>
-      </c>
-      <c r="R23" s="51"/>
+      <c r="N23" s="37">
+        <v>100</v>
+      </c>
+      <c r="O23" s="60" t="s">
+        <v>363</v>
+      </c>
+      <c r="P23" s="38">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q23" s="38">
+        <f>P23*N23</f>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R23" s="37"/>
       <c r="S23" s="59"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="46">
-        <f>ROW(B24) - ROW($B$9)</f>
+      <c r="B24" s="47">
+        <f t="shared" ref="B24" si="13">ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="F24" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="G24" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="H24" s="37" t="s">
-        <v>249</v>
-      </c>
-      <c r="I24" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="J24" s="37" t="s">
-        <v>290</v>
+      <c r="C24" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="51" t="s">
+        <v>386</v>
+      </c>
+      <c r="E24" s="51" t="s">
+        <v>396</v>
+      </c>
+      <c r="F24" s="51" t="s">
+        <v>393</v>
+      </c>
+      <c r="G24" s="51" t="s">
+        <v>389</v>
+      </c>
+      <c r="H24" s="51" t="s">
+        <v>243</v>
+      </c>
+      <c r="I24" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="J24" s="51" t="s">
+        <v>397</v>
       </c>
       <c r="K24" s="51" t="s">
-        <v>365</v>
-      </c>
-      <c r="L24" s="37">
-        <v>2</v>
-      </c>
-      <c r="M24" s="37">
-        <f>L24*5</f>
-        <v>10</v>
-      </c>
-      <c r="N24" s="37">
-        <v>20</v>
+        <v>398</v>
+      </c>
+      <c r="L24" s="51">
+        <v>1</v>
+      </c>
+      <c r="M24" s="51">
+        <f t="shared" ref="M24" si="14">L24*5</f>
+        <v>5</v>
+      </c>
+      <c r="N24" s="51">
+        <v>100</v>
       </c>
       <c r="O24" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P24" s="38">
-        <v>9.1000000000000004E-3</v>
-      </c>
-      <c r="Q24" s="38">
-        <f>P24*N24</f>
-        <v>0.182</v>
-      </c>
-      <c r="R24" s="37"/>
+        <v>363</v>
+      </c>
+      <c r="P24" s="52">
+        <v>1.8E-3</v>
+      </c>
+      <c r="Q24" s="52">
+        <f t="shared" ref="Q24" si="15">P24*N24</f>
+        <v>0.18</v>
+      </c>
+      <c r="R24" s="51"/>
       <c r="S24" s="59"/>
     </row>
     <row r="25" spans="1:19" ht="24" x14ac:dyDescent="0.25">
@@ -3360,51 +3438,51 @@
         <v>16</v>
       </c>
       <c r="C25" s="54" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G25" s="51" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="H25" s="51" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="I25" s="51" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J25" s="51" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="K25" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="L25" s="51">
         <v>1</v>
       </c>
       <c r="M25" s="51">
-        <f t="shared" ref="M25" si="15">L25*5</f>
+        <f t="shared" ref="M25" si="16">L25*5</f>
         <v>5</v>
       </c>
       <c r="N25" s="51">
         <v>10</v>
       </c>
       <c r="O25" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P25" s="52">
-        <v>3.4200000000000001E-2</v>
+        <v>4.4600000000000001E-2</v>
       </c>
       <c r="Q25" s="52">
-        <f t="shared" ref="Q25" si="16">P25*N25</f>
-        <v>0.34200000000000003</v>
+        <f t="shared" ref="Q25" si="17">P25*N25</f>
+        <v>0.44600000000000001</v>
       </c>
       <c r="R25" s="51"/>
       <c r="S25" s="59"/>
@@ -3419,109 +3497,109 @@
         <v>11</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J26" s="37" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="K26" s="51" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="L26" s="37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" s="37">
         <f>L26*5</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N26" s="37">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O26" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P26" s="38">
-        <v>7.7499999999999999E-2</v>
+        <v>9.1000000000000004E-3</v>
       </c>
       <c r="Q26" s="38">
         <f>P26*N26</f>
-        <v>0.77500000000000002</v>
+        <v>0.182</v>
       </c>
       <c r="R26" s="37"/>
       <c r="S26" s="59"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="47">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C27" s="54" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D27" s="51" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G27" s="51" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="H27" s="51" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J27" s="51" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="K27" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="L27" s="51">
         <v>1</v>
       </c>
       <c r="M27" s="51">
-        <f t="shared" ref="M27" si="17">L27*5</f>
+        <f t="shared" ref="M27" si="18">L27*5</f>
         <v>5</v>
       </c>
       <c r="N27" s="51">
         <v>10</v>
       </c>
       <c r="O27" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P27" s="52">
-        <v>5.4399999999999997E-2</v>
+        <v>3.4200000000000001E-2</v>
       </c>
       <c r="Q27" s="52">
-        <f t="shared" ref="Q27" si="18">P27*N27</f>
-        <v>0.54399999999999993</v>
+        <f t="shared" ref="Q27" si="19">P27*N27</f>
+        <v>0.34200000000000003</v>
       </c>
       <c r="R27" s="51"/>
       <c r="S27" s="59"/>
     </row>
-    <row r="28" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="46">
         <f>ROW(B28) - ROW($B$9)</f>
@@ -3531,28 +3609,28 @@
         <v>11</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>294</v>
-      </c>
-      <c r="K28" s="37" t="s">
-        <v>365</v>
+        <v>287</v>
+      </c>
+      <c r="K28" s="51" t="s">
+        <v>360</v>
       </c>
       <c r="L28" s="37">
         <v>1</v>
@@ -3565,19 +3643,19 @@
         <v>10</v>
       </c>
       <c r="O28" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P28" s="38">
-        <v>8.6400000000000005E-2</v>
+        <v>7.7499999999999999E-2</v>
       </c>
       <c r="Q28" s="38">
         <f>P28*N28</f>
-        <v>0.8640000000000001</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="R28" s="37"/>
       <c r="S28" s="59"/>
     </row>
-    <row r="29" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="47">
         <f t="shared" si="0"/>
@@ -3587,53 +3665,53 @@
         <v>11</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G29" s="51" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="H29" s="51" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J29" s="51" t="s">
-        <v>295</v>
-      </c>
-      <c r="K29" s="51" t="s">
-        <v>365</v>
+        <v>288</v>
+      </c>
+      <c r="K29" s="37" t="s">
+        <v>360</v>
       </c>
       <c r="L29" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M29" s="51">
-        <f t="shared" ref="M29" si="19">L29*5</f>
+        <f t="shared" ref="M29" si="20">L29*5</f>
+        <v>5</v>
+      </c>
+      <c r="N29" s="51">
         <v>10</v>
       </c>
-      <c r="N29" s="51">
-        <v>20</v>
-      </c>
       <c r="O29" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P29" s="52">
-        <v>3.1699999999999999E-2</v>
+        <v>5.4399999999999997E-2</v>
       </c>
       <c r="Q29" s="52">
-        <f t="shared" ref="Q29" si="20">P29*N29</f>
-        <v>0.63400000000000001</v>
+        <f t="shared" ref="Q29" si="21">P29*N29</f>
+        <v>0.54399999999999993</v>
       </c>
       <c r="R29" s="51"/>
       <c r="S29" s="59"/>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="46">
         <f>ROW(B30) - ROW($B$9)</f>
@@ -3643,51 +3721,53 @@
         <v>11</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>255</v>
-      </c>
-      <c r="I30" s="37"/>
+        <v>249</v>
+      </c>
+      <c r="I30" s="37" t="s">
+        <v>360</v>
+      </c>
       <c r="J30" s="37" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="L30" s="37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M30" s="37">
         <f>L30*5</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="N30" s="37">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O30" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P30" s="38">
-        <v>0.1351</v>
+        <v>8.6400000000000005E-2</v>
       </c>
       <c r="Q30" s="38">
         <f>P30*N30</f>
-        <v>2.702</v>
+        <v>0.8640000000000001</v>
       </c>
       <c r="R30" s="37"/>
       <c r="S30" s="59"/>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="47">
         <f t="shared" si="0"/>
@@ -3697,165 +3777,163 @@
         <v>11</v>
       </c>
       <c r="D31" s="51" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G31" s="51" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="H31" s="51" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="I31" s="51" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J31" s="51" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="K31" s="51" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="L31" s="51">
         <v>2</v>
       </c>
       <c r="M31" s="51">
-        <f t="shared" ref="M31" si="21">L31*5</f>
+        <f t="shared" ref="M31" si="22">L31*5</f>
         <v>10</v>
       </c>
       <c r="N31" s="51">
         <v>20</v>
       </c>
       <c r="O31" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P31" s="52">
-        <v>4.7500000000000001E-2</v>
+        <v>3.1699999999999999E-2</v>
       </c>
       <c r="Q31" s="52">
-        <f t="shared" ref="Q31" si="22">P31*N31</f>
-        <v>0.95</v>
+        <f t="shared" ref="Q31" si="23">P31*N31</f>
+        <v>0.63400000000000001</v>
       </c>
       <c r="R31" s="51"/>
       <c r="S31" s="59"/>
     </row>
-    <row r="32" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="46">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
       <c r="C32" s="53" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E32" s="37" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>257</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>365</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="I32" s="37"/>
       <c r="J32" s="37" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="K32" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="L32" s="37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M32" s="37">
         <f>L32*5</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N32" s="37">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O32" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P32" s="38">
-        <v>6.83E-2</v>
+        <v>0.1351</v>
       </c>
       <c r="Q32" s="38">
         <f>P32*N32</f>
-        <v>0.68300000000000005</v>
+        <v>2.702</v>
       </c>
       <c r="R32" s="37"/>
       <c r="S32" s="59"/>
     </row>
-    <row r="33" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="47">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="C33" s="54" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D33" s="51" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F33" s="51" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="G33" s="51" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="H33" s="51" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="I33" s="51" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J33" s="51" t="s">
-        <v>299</v>
-      </c>
-      <c r="K33" s="37" t="s">
-        <v>365</v>
+        <v>292</v>
+      </c>
+      <c r="K33" s="51" t="s">
+        <v>360</v>
       </c>
       <c r="L33" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33" s="51">
-        <f t="shared" ref="M33" si="23">L33*5</f>
-        <v>5</v>
+        <f t="shared" ref="M33" si="24">L33*5</f>
+        <v>10</v>
       </c>
       <c r="N33" s="51">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O33" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P33" s="52">
-        <v>4.5100000000000001E-2</v>
+        <v>4.7500000000000001E-2</v>
       </c>
       <c r="Q33" s="52">
-        <f t="shared" ref="Q33" si="24">P33*N33</f>
-        <v>0.45100000000000001</v>
+        <f t="shared" ref="Q33" si="25">P33*N33</f>
+        <v>0.95</v>
       </c>
       <c r="R33" s="51"/>
       <c r="S33" s="59"/>
     </row>
-    <row r="34" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" ht="24" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="46">
         <f>ROW(B34) - ROW($B$9)</f>
@@ -3865,361 +3943,364 @@
         <v>13</v>
       </c>
       <c r="D34" s="37" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E34" s="37" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J34" s="37" t="s">
-        <v>300</v>
-      </c>
-      <c r="K34" s="51" t="s">
-        <v>365</v>
+        <v>293</v>
+      </c>
+      <c r="K34" s="37" t="s">
+        <v>360</v>
       </c>
       <c r="L34" s="37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M34" s="37">
         <f>L34*5</f>
+        <v>5</v>
+      </c>
+      <c r="N34" s="37">
         <v>10</v>
       </c>
-      <c r="N34" s="37">
-        <v>20</v>
-      </c>
       <c r="O34" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P34" s="38">
-        <v>5.8999999999999997E-2</v>
+        <v>6.83E-2</v>
       </c>
       <c r="Q34" s="38">
         <f>P34*N34</f>
-        <v>1.18</v>
+        <v>0.68300000000000005</v>
       </c>
       <c r="R34" s="37"/>
       <c r="S34" s="59"/>
     </row>
-    <row r="35" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" ht="24" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="47">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="C35" s="54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D35" s="51" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F35" s="51" t="s">
-        <v>366</v>
+        <v>163</v>
       </c>
       <c r="G35" s="51" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="H35" s="51" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="I35" s="51" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J35" s="51" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="K35" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="L35" s="51">
         <v>1</v>
       </c>
       <c r="M35" s="51">
-        <f t="shared" ref="M35" si="25">L35*5</f>
+        <f t="shared" ref="M35" si="26">L35*5</f>
         <v>5</v>
       </c>
       <c r="N35" s="51">
         <v>10</v>
       </c>
       <c r="O35" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P35" s="52">
-        <v>0.1769</v>
+        <v>4.5100000000000001E-2</v>
       </c>
       <c r="Q35" s="52">
-        <f t="shared" ref="Q35" si="26">P35*N35</f>
-        <v>1.7690000000000001</v>
+        <f t="shared" ref="Q35" si="27">P35*N35</f>
+        <v>0.45100000000000001</v>
       </c>
       <c r="R35" s="51"/>
       <c r="S35" s="59"/>
     </row>
-    <row r="36" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" ht="24" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="46">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
       <c r="C36" s="53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D36" s="37" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E36" s="37" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>366</v>
+        <v>164</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J36" s="37" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="K36" s="51" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="L36" s="37">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M36" s="37">
         <f>L36*5</f>
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="N36" s="37">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O36" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P36" s="38">
-        <v>0.21840000000000001</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="Q36" s="38">
         <f>P36*N36</f>
-        <v>6.5520000000000005</v>
+        <v>1.18</v>
       </c>
       <c r="R36" s="37"/>
       <c r="S36" s="59"/>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" ht="48" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="47">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="53" t="s">
-        <v>15</v>
+      <c r="C37" s="54" t="s">
+        <v>14</v>
       </c>
       <c r="D37" s="51" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E37" s="51" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F37" s="51" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="G37" s="51" t="s">
-        <v>212</v>
+        <v>165</v>
       </c>
       <c r="H37" s="51" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="I37" s="51" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J37" s="51" t="s">
-        <v>376</v>
+        <v>296</v>
       </c>
       <c r="K37" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="L37" s="51">
         <v>1</v>
       </c>
       <c r="M37" s="51">
-        <f t="shared" ref="M37" si="27">L37*5</f>
+        <f t="shared" ref="M37" si="28">L37*5</f>
         <v>5</v>
       </c>
       <c r="N37" s="51">
         <v>10</v>
       </c>
       <c r="O37" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P37" s="52">
-        <v>0.3211</v>
+        <v>0.1769</v>
       </c>
       <c r="Q37" s="52">
-        <f t="shared" ref="Q37" si="28">P37*N37</f>
-        <v>3.2109999999999999</v>
+        <f t="shared" ref="Q37" si="29">P37*N37</f>
+        <v>1.7690000000000001</v>
       </c>
       <c r="R37" s="51"/>
       <c r="S37" s="59"/>
     </row>
-    <row r="38" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" ht="48" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="46">
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
       <c r="C38" s="53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>213</v>
+        <v>166</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J38" s="37" t="s">
-        <v>213</v>
-      </c>
-      <c r="K38" s="37" t="s">
-        <v>365</v>
+        <v>297</v>
+      </c>
+      <c r="K38" s="51" t="s">
+        <v>360</v>
       </c>
       <c r="L38" s="37">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M38" s="37">
         <f>L38*5</f>
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="N38" s="37">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="O38" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P38" s="38">
-        <v>7.0400000000000004E-2</v>
+        <v>0.21840000000000001</v>
       </c>
       <c r="Q38" s="38">
         <f>P38*N38</f>
-        <v>0.8448</v>
+        <v>6.5520000000000005</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="59"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" ht="48" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="47">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="54" t="s">
-        <v>16</v>
-      </c>
-      <c r="D39" s="75" t="s">
-        <v>56</v>
-      </c>
-      <c r="E39" s="75" t="s">
-        <v>119</v>
-      </c>
-      <c r="F39" s="64" t="s">
-        <v>366</v>
-      </c>
-      <c r="G39" s="75" t="s">
-        <v>214</v>
-      </c>
-      <c r="H39" s="64" t="s">
-        <v>365</v>
-      </c>
-      <c r="I39" s="64" t="s">
-        <v>365</v>
-      </c>
-      <c r="J39" s="64" t="s">
-        <v>365</v>
-      </c>
-      <c r="K39" s="75" t="s">
-        <v>365</v>
-      </c>
-      <c r="L39" s="75">
-        <v>2</v>
-      </c>
-      <c r="M39" s="75">
-        <f t="shared" ref="M39" si="29">L39*5</f>
+      <c r="C39" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="E39" s="37" t="s">
+        <v>399</v>
+      </c>
+      <c r="F39" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="G39" s="37" t="s">
+        <v>390</v>
+      </c>
+      <c r="H39" s="37" t="s">
+        <v>400</v>
+      </c>
+      <c r="I39" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="J39" s="37" t="s">
+        <v>401</v>
+      </c>
+      <c r="K39" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="L39" s="37">
+        <v>1</v>
+      </c>
+      <c r="M39" s="37">
+        <f>L39*5</f>
+        <v>5</v>
+      </c>
+      <c r="N39" s="51">
         <v>10</v>
       </c>
-      <c r="N39" s="75" t="s">
-        <v>365</v>
-      </c>
-      <c r="O39" s="75" t="s">
-        <v>365</v>
-      </c>
-      <c r="P39" s="76" t="s">
-        <v>365</v>
-      </c>
-      <c r="Q39" s="76" t="s">
-        <v>365</v>
-      </c>
-      <c r="R39" s="78" t="s">
-        <v>380</v>
-      </c>
+      <c r="O39" s="63" t="s">
+        <v>363</v>
+      </c>
+      <c r="P39" s="52">
+        <v>0.14860000000000001</v>
+      </c>
+      <c r="Q39" s="38">
+        <f>P39*N39</f>
+        <v>1.4860000000000002</v>
+      </c>
+      <c r="R39" s="51"/>
       <c r="S39" s="59"/>
     </row>
-    <row r="40" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" ht="24" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="46">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
       <c r="C40" s="53" t="s">
-        <v>388</v>
+        <v>15</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>384</v>
+        <v>115</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>386</v>
+        <v>209</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>387</v>
-      </c>
-      <c r="I40" s="37"/>
-      <c r="J40" s="37"/>
+        <v>257</v>
+      </c>
+      <c r="I40" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="J40" s="37" t="s">
+        <v>209</v>
+      </c>
       <c r="K40" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="L40" s="37">
         <v>1</v>
@@ -4228,1921 +4309,2159 @@
         <f>L40*5</f>
         <v>5</v>
       </c>
-      <c r="N40" s="37"/>
-      <c r="O40" s="37"/>
-      <c r="P40" s="38"/>
+      <c r="N40" s="37">
+        <v>12</v>
+      </c>
+      <c r="O40" s="63" t="s">
+        <v>363</v>
+      </c>
+      <c r="P40" s="38">
+        <v>7.0400000000000004E-2</v>
+      </c>
       <c r="Q40" s="38">
         <f>P40*N40</f>
-        <v>0</v>
+        <v>0.8448</v>
       </c>
       <c r="R40" s="37"/>
       <c r="S40" s="59"/>
     </row>
-    <row r="41" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="47">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="C41" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="D41" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="E41" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="F41" s="37" t="s">
-        <v>366</v>
-      </c>
-      <c r="G41" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="H41" s="51" t="s">
-        <v>263</v>
-      </c>
-      <c r="I41" s="51" t="s">
-        <v>365</v>
-      </c>
-      <c r="J41" s="51" t="s">
-        <v>303</v>
-      </c>
-      <c r="K41" s="51" t="s">
-        <v>365</v>
-      </c>
-      <c r="L41" s="51">
-        <v>1</v>
-      </c>
-      <c r="M41" s="51">
+        <v>16</v>
+      </c>
+      <c r="D41" s="75" t="s">
+        <v>54</v>
+      </c>
+      <c r="E41" s="75" t="s">
+        <v>116</v>
+      </c>
+      <c r="F41" s="64" t="s">
+        <v>361</v>
+      </c>
+      <c r="G41" s="75" t="s">
+        <v>210</v>
+      </c>
+      <c r="H41" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="I41" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="J41" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="K41" s="75" t="s">
+        <v>360</v>
+      </c>
+      <c r="L41" s="75">
+        <v>2</v>
+      </c>
+      <c r="M41" s="75">
         <f t="shared" ref="M41" si="30">L41*5</f>
-        <v>5</v>
-      </c>
-      <c r="N41" s="51">
-        <v>6</v>
-      </c>
-      <c r="O41" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P41" s="52">
-        <v>0.67300000000000004</v>
-      </c>
-      <c r="Q41" s="52">
-        <f t="shared" ref="Q41" si="31">P41*N41</f>
-        <v>4.0380000000000003</v>
-      </c>
-      <c r="R41" s="51"/>
+        <v>10</v>
+      </c>
+      <c r="N41" s="75" t="s">
+        <v>360</v>
+      </c>
+      <c r="O41" s="75" t="s">
+        <v>360</v>
+      </c>
+      <c r="P41" s="76" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q41" s="76" t="s">
+        <v>360</v>
+      </c>
+      <c r="R41" s="78" t="s">
+        <v>374</v>
+      </c>
       <c r="S41" s="59"/>
     </row>
-    <row r="42" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="65"/>
-      <c r="B42" s="66">
+    <row r="42" spans="1:26" ht="24" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="B42" s="46">
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="67" t="s">
-        <v>18</v>
-      </c>
-      <c r="D42" s="68" t="s">
-        <v>59</v>
-      </c>
-      <c r="E42" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="F42" s="68" t="s">
-        <v>366</v>
-      </c>
-      <c r="G42" s="68" t="s">
-        <v>171</v>
-      </c>
-      <c r="H42" s="68" t="s">
-        <v>264</v>
-      </c>
-      <c r="I42" s="69" t="s">
-        <v>365</v>
-      </c>
-      <c r="J42" s="69" t="s">
-        <v>365</v>
-      </c>
-      <c r="K42" s="69" t="s">
-        <v>365</v>
-      </c>
-      <c r="L42" s="68">
+      <c r="C42" s="53" t="s">
+        <v>382</v>
+      </c>
+      <c r="D42" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="F42" s="37" t="s">
+        <v>379</v>
+      </c>
+      <c r="G42" s="37" t="s">
+        <v>380</v>
+      </c>
+      <c r="H42" s="37" t="s">
+        <v>381</v>
+      </c>
+      <c r="I42" s="37"/>
+      <c r="J42" s="37"/>
+      <c r="K42" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="L42" s="37">
         <v>1</v>
       </c>
-      <c r="M42" s="68">
+      <c r="M42" s="37">
         <f>L42*5</f>
         <v>5</v>
       </c>
-      <c r="N42" s="68">
-        <v>6</v>
-      </c>
-      <c r="O42" s="70" t="s">
-        <v>377</v>
-      </c>
-      <c r="P42" s="71">
-        <v>1.01</v>
-      </c>
-      <c r="Q42" s="72">
+      <c r="N42" s="37"/>
+      <c r="O42" s="37"/>
+      <c r="P42" s="38"/>
+      <c r="Q42" s="38">
         <f>P42*N42</f>
-        <v>6.0600000000000005</v>
-      </c>
-      <c r="R42" s="68"/>
-      <c r="S42" s="73"/>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="R42" s="37"/>
+      <c r="S42" s="59"/>
+    </row>
+    <row r="43" spans="1:26" ht="48" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="47">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="C43" s="54" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D43" s="51" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E43" s="51" t="s">
-        <v>381</v>
-      </c>
-      <c r="F43" s="51" t="s">
-        <v>382</v>
+        <v>117</v>
+      </c>
+      <c r="F43" s="37" t="s">
+        <v>361</v>
       </c>
       <c r="G43" s="51" t="s">
-        <v>382</v>
+        <v>167</v>
       </c>
       <c r="H43" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="I43" s="51"/>
+        <v>258</v>
+      </c>
+      <c r="I43" s="51" t="s">
+        <v>360</v>
+      </c>
       <c r="J43" s="51" t="s">
-        <v>383</v>
+        <v>298</v>
       </c>
       <c r="K43" s="51" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="L43" s="51">
         <v>1</v>
       </c>
       <c r="M43" s="51">
-        <f t="shared" ref="M43" si="32">L43*5</f>
+        <f t="shared" ref="M43" si="31">L43*5</f>
         <v>5</v>
       </c>
-      <c r="N43" s="51"/>
-      <c r="O43" s="51"/>
-      <c r="P43" s="52"/>
+      <c r="N43" s="51">
+        <v>6</v>
+      </c>
+      <c r="O43" s="63" t="s">
+        <v>363</v>
+      </c>
+      <c r="P43" s="52">
+        <v>0.67300000000000004</v>
+      </c>
       <c r="Q43" s="52">
-        <f t="shared" ref="Q43" si="33">P43*N43</f>
-        <v>0</v>
+        <f t="shared" ref="Q43" si="32">P43*N43</f>
+        <v>4.0380000000000003</v>
       </c>
       <c r="R43" s="51"/>
       <c r="S43" s="59"/>
     </row>
-    <row r="44" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A44" s="1"/>
-      <c r="B44" s="46">
+    <row r="44" spans="1:26" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="65"/>
+      <c r="B44" s="66">
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="D44" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="E44" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="F44" s="37" t="s">
-        <v>366</v>
-      </c>
-      <c r="G44" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="H44" s="37" t="s">
-        <v>266</v>
-      </c>
-      <c r="I44" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="J44" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="K44" s="37" t="s">
-        <v>339</v>
-      </c>
-      <c r="L44" s="37">
+      <c r="C44" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="E44" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F44" s="68" t="s">
+        <v>361</v>
+      </c>
+      <c r="G44" s="68" t="s">
+        <v>168</v>
+      </c>
+      <c r="H44" s="68" t="s">
+        <v>259</v>
+      </c>
+      <c r="I44" s="69" t="s">
+        <v>360</v>
+      </c>
+      <c r="J44" s="69" t="s">
+        <v>360</v>
+      </c>
+      <c r="K44" s="69" t="s">
+        <v>360</v>
+      </c>
+      <c r="L44" s="68">
         <v>1</v>
       </c>
-      <c r="M44" s="37">
+      <c r="M44" s="68">
         <f>L44*5</f>
         <v>5</v>
       </c>
-      <c r="N44" s="37">
-        <v>10</v>
-      </c>
-      <c r="O44" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P44" s="38">
-        <v>8.5300000000000001E-2</v>
-      </c>
-      <c r="Q44" s="38">
+      <c r="N44" s="68">
+        <v>6</v>
+      </c>
+      <c r="O44" s="70" t="s">
+        <v>371</v>
+      </c>
+      <c r="P44" s="71">
+        <v>1.01</v>
+      </c>
+      <c r="Q44" s="72">
         <f>P44*N44</f>
-        <v>0.85299999999999998</v>
-      </c>
-      <c r="R44" s="37"/>
-      <c r="S44" s="59"/>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+        <v>6.0600000000000005</v>
+      </c>
+      <c r="R44" s="68"/>
+      <c r="S44" s="73"/>
+      <c r="U44"/>
+      <c r="V44"/>
+      <c r="W44"/>
+      <c r="X44"/>
+      <c r="Y44"/>
+      <c r="Z44"/>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="47">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="53" t="s">
+      <c r="C45" s="54" t="s">
         <v>19</v>
       </c>
       <c r="D45" s="51" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E45" s="51" t="s">
-        <v>123</v>
+        <v>375</v>
       </c>
       <c r="F45" s="51" t="s">
-        <v>172</v>
+        <v>376</v>
       </c>
       <c r="G45" s="51" t="s">
-        <v>216</v>
+        <v>376</v>
       </c>
       <c r="H45" s="51" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="I45" s="51" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J45" s="51" t="s">
-        <v>305</v>
+        <v>377</v>
       </c>
       <c r="K45" s="51" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="L45" s="51">
         <v>1</v>
       </c>
       <c r="M45" s="51">
-        <f t="shared" ref="M45" si="34">L45*5</f>
+        <f t="shared" ref="M45" si="33">L45*5</f>
         <v>5</v>
       </c>
       <c r="N45" s="51">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="O45" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P45" s="52">
-        <v>8.3000000000000001E-3</v>
+        <v>0.21360000000000001</v>
       </c>
       <c r="Q45" s="52">
-        <f t="shared" ref="Q45" si="35">P45*N45</f>
-        <v>0.41499999999999998</v>
+        <f t="shared" ref="Q45" si="34">P45*N45</f>
+        <v>2.1360000000000001</v>
       </c>
       <c r="R45" s="51"/>
       <c r="S45" s="59"/>
     </row>
-    <row r="46" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" ht="24" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="46">
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
       <c r="C46" s="53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>173</v>
+        <v>361</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>365</v>
+        <v>334</v>
       </c>
       <c r="L46" s="37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M46" s="37">
         <f>L46*5</f>
-        <v>15</v>
-      </c>
-      <c r="N46" s="51">
-        <v>20</v>
+        <v>5</v>
+      </c>
+      <c r="N46" s="37">
+        <v>10</v>
       </c>
       <c r="O46" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P46" s="52">
-        <v>5.1499999999999997E-2</v>
+        <v>363</v>
+      </c>
+      <c r="P46" s="38">
+        <v>8.5300000000000001E-2</v>
       </c>
       <c r="Q46" s="38">
         <f>P46*N46</f>
-        <v>1.03</v>
+        <v>0.85299999999999998</v>
       </c>
       <c r="R46" s="37"/>
       <c r="S46" s="59"/>
     </row>
-    <row r="47" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="47">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="54" t="s">
-        <v>20</v>
+      <c r="C47" s="53" t="s">
+        <v>19</v>
       </c>
       <c r="D47" s="51" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E47" s="51" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F47" s="51" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G47" s="51" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="H47" s="51" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="I47" s="51" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J47" s="51" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="K47" s="51" t="s">
-        <v>365</v>
+        <v>335</v>
       </c>
       <c r="L47" s="51">
         <v>1</v>
       </c>
       <c r="M47" s="51">
-        <f t="shared" ref="M47" si="36">L47*5</f>
+        <f t="shared" ref="M47:M48" si="35">L47*5</f>
         <v>5</v>
       </c>
       <c r="N47" s="51">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="O47" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P47" s="52">
-        <v>3.1300000000000001E-2</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="Q47" s="52">
-        <f t="shared" ref="Q47" si="37">P47*N47</f>
-        <v>0.626</v>
+        <f t="shared" ref="Q47:Q48" si="36">P47*N47</f>
+        <v>0.41499999999999998</v>
       </c>
       <c r="R47" s="51"/>
       <c r="S47" s="59"/>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" ht="24" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
-      <c r="B48" s="46">
-        <f>ROW(B48) - ROW($B$9)</f>
+      <c r="B48" s="47">
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="C48" s="53" t="s">
-        <v>378</v>
-      </c>
-      <c r="D48" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="E48" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="F48" s="64" t="s">
-        <v>366</v>
-      </c>
-      <c r="G48" s="64" t="s">
-        <v>174</v>
-      </c>
-      <c r="H48" s="64" t="s">
-        <v>365</v>
-      </c>
-      <c r="I48" s="64" t="s">
-        <v>365</v>
-      </c>
-      <c r="J48" s="64" t="s">
-        <v>365</v>
-      </c>
-      <c r="K48" s="64" t="s">
-        <v>365</v>
-      </c>
-      <c r="L48" s="64">
-        <v>4</v>
-      </c>
-      <c r="M48" s="64">
-        <f>L48*5</f>
+        <v>19</v>
+      </c>
+      <c r="D48" s="51" t="s">
+        <v>387</v>
+      </c>
+      <c r="E48" s="51" t="s">
+        <v>402</v>
+      </c>
+      <c r="F48" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="G48" s="51" t="s">
+        <v>391</v>
+      </c>
+      <c r="H48" s="51" t="s">
+        <v>403</v>
+      </c>
+      <c r="I48" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="J48" s="51" t="s">
+        <v>404</v>
+      </c>
+      <c r="K48" s="51" t="s">
+        <v>405</v>
+      </c>
+      <c r="L48" s="51">
+        <v>1</v>
+      </c>
+      <c r="M48" s="51">
+        <f t="shared" si="35"/>
+        <v>5</v>
+      </c>
+      <c r="N48" s="51">
+        <v>10</v>
+      </c>
+      <c r="O48" s="63" t="s">
+        <v>363</v>
+      </c>
+      <c r="P48" s="52">
+        <v>3.4299999999999997E-2</v>
+      </c>
+      <c r="Q48" s="52">
+        <f t="shared" si="36"/>
+        <v>0.34299999999999997</v>
+      </c>
+      <c r="R48" s="51"/>
+      <c r="S48" s="59"/>
+    </row>
+    <row r="49" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="B49" s="46">
+        <f>ROW(B49) - ROW($B$9)</f>
+        <v>40</v>
+      </c>
+      <c r="C49" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="N48" s="64"/>
-      <c r="O48" s="75" t="s">
-        <v>365</v>
-      </c>
-      <c r="P48" s="77" t="s">
-        <v>365</v>
-      </c>
-      <c r="Q48" s="77" t="s">
-        <v>365</v>
-      </c>
-      <c r="R48" s="78" t="s">
-        <v>380</v>
-      </c>
-      <c r="S48" s="59"/>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="1"/>
-      <c r="B49" s="47">
+      <c r="D49" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="E49" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F49" s="37" t="s">
+        <v>170</v>
+      </c>
+      <c r="G49" s="37" t="s">
+        <v>213</v>
+      </c>
+      <c r="H49" s="37" t="s">
+        <v>263</v>
+      </c>
+      <c r="I49" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="J49" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="K49" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="L49" s="37">
+        <v>3</v>
+      </c>
+      <c r="M49" s="37">
+        <f>L49*5</f>
+        <v>15</v>
+      </c>
+      <c r="N49" s="51">
+        <v>20</v>
+      </c>
+      <c r="O49" s="63" t="s">
+        <v>363</v>
+      </c>
+      <c r="P49" s="52">
+        <v>5.1499999999999997E-2</v>
+      </c>
+      <c r="Q49" s="38">
+        <f>P49*N49</f>
+        <v>1.03</v>
+      </c>
+      <c r="R49" s="37"/>
+      <c r="S49" s="59"/>
+    </row>
+    <row r="50" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="47">
         <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="C49" s="54" t="s">
-        <v>21</v>
-      </c>
-      <c r="D49" s="51" t="s">
-        <v>66</v>
-      </c>
-      <c r="E49" s="51" t="s">
-        <v>127</v>
-      </c>
-      <c r="F49" s="51" t="s">
-        <v>175</v>
-      </c>
-      <c r="G49" s="51" t="s">
-        <v>219</v>
-      </c>
-      <c r="H49" s="51" t="s">
-        <v>249</v>
-      </c>
-      <c r="I49" s="51" t="s">
-        <v>365</v>
-      </c>
-      <c r="J49" s="51" t="s">
-        <v>308</v>
-      </c>
-      <c r="K49" s="51" t="s">
-        <v>365</v>
-      </c>
-      <c r="L49" s="51">
-        <v>6</v>
-      </c>
-      <c r="M49" s="51">
-        <f t="shared" ref="M49" si="38">L49*5</f>
-        <v>30</v>
-      </c>
-      <c r="N49" s="51">
-        <v>40</v>
-      </c>
-      <c r="O49" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P49" s="52">
-        <v>2.1899999999999999E-2</v>
-      </c>
-      <c r="Q49" s="52">
-        <f t="shared" ref="Q49" si="39">P49*N49</f>
-        <v>0.876</v>
-      </c>
-      <c r="R49" s="51"/>
-      <c r="S49" s="59"/>
-    </row>
-    <row r="50" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
-      <c r="B50" s="46">
-        <f>ROW(B50) - ROW($B$9)</f>
         <v>41</v>
       </c>
-      <c r="C50" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="D50" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="E50" s="37" t="s">
-        <v>128</v>
-      </c>
-      <c r="F50" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="G50" s="37" t="s">
-        <v>220</v>
-      </c>
-      <c r="H50" s="37" t="s">
-        <v>253</v>
-      </c>
-      <c r="I50" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="J50" s="37" t="s">
-        <v>309</v>
-      </c>
-      <c r="K50" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="L50" s="37">
+      <c r="C50" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="E50" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="F50" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="G50" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="H50" s="51" t="s">
+        <v>263</v>
+      </c>
+      <c r="I50" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="J50" s="51" t="s">
+        <v>302</v>
+      </c>
+      <c r="K50" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="L50" s="51">
         <v>1</v>
       </c>
-      <c r="M50" s="37">
-        <f>L50*5</f>
+      <c r="M50" s="51">
+        <f t="shared" ref="M50" si="37">L50*5</f>
         <v>5</v>
       </c>
-      <c r="N50" s="37">
-        <v>10</v>
+      <c r="N50" s="51">
+        <v>20</v>
       </c>
       <c r="O50" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P50" s="38">
-        <v>3.1099999999999999E-2</v>
-      </c>
-      <c r="Q50" s="38">
-        <f>P50*N50</f>
-        <v>0.311</v>
-      </c>
-      <c r="R50" s="37"/>
+        <v>363</v>
+      </c>
+      <c r="P50" s="52">
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="Q50" s="52">
+        <f t="shared" ref="Q50" si="38">P50*N50</f>
+        <v>0.626</v>
+      </c>
+      <c r="R50" s="51"/>
       <c r="S50" s="59"/>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
-      <c r="B51" s="47">
-        <f t="shared" si="0"/>
+      <c r="B51" s="46">
+        <f>ROW(B51) - ROW($B$9)</f>
         <v>42</v>
       </c>
-      <c r="C51" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="D51" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="E51" s="51" t="s">
-        <v>129</v>
-      </c>
-      <c r="F51" s="51" t="s">
-        <v>176</v>
-      </c>
-      <c r="G51" s="51" t="s">
-        <v>221</v>
-      </c>
-      <c r="H51" s="51" t="s">
-        <v>247</v>
-      </c>
-      <c r="I51" s="51" t="s">
-        <v>365</v>
-      </c>
-      <c r="J51" s="51" t="s">
-        <v>310</v>
-      </c>
-      <c r="K51" s="51" t="s">
-        <v>341</v>
-      </c>
-      <c r="L51" s="51">
-        <v>1</v>
-      </c>
-      <c r="M51" s="51">
-        <f t="shared" ref="M51" si="40">L51*5</f>
-        <v>5</v>
-      </c>
-      <c r="N51" s="51">
-        <v>100</v>
-      </c>
-      <c r="O51" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P51" s="52">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="Q51" s="52">
-        <f t="shared" ref="Q51" si="41">P51*N51</f>
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="R51" s="51"/>
+      <c r="C51" s="53" t="s">
+        <v>372</v>
+      </c>
+      <c r="D51" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="E51" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="F51" s="64" t="s">
+        <v>361</v>
+      </c>
+      <c r="G51" s="64" t="s">
+        <v>171</v>
+      </c>
+      <c r="H51" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="I51" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="J51" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="K51" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="L51" s="64">
+        <v>4</v>
+      </c>
+      <c r="M51" s="64">
+        <f>L51*5</f>
+        <v>20</v>
+      </c>
+      <c r="N51" s="64"/>
+      <c r="O51" s="75" t="s">
+        <v>360</v>
+      </c>
+      <c r="P51" s="77" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q51" s="77" t="s">
+        <v>360</v>
+      </c>
+      <c r="R51" s="78" t="s">
+        <v>374</v>
+      </c>
       <c r="S51" s="59"/>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
-      <c r="B52" s="46">
-        <f>ROW(B52) - ROW($B$9)</f>
+      <c r="B52" s="47">
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="C52" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="D52" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="E52" s="37" t="s">
-        <v>130</v>
-      </c>
-      <c r="F52" s="37" t="s">
-        <v>177</v>
-      </c>
-      <c r="G52" s="64" t="s">
-        <v>222</v>
+        <v>21</v>
+      </c>
+      <c r="D52" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="F52" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="G52" s="51" t="s">
+        <v>215</v>
       </c>
       <c r="H52" s="51" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I52" s="51" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="J52" s="51" t="s">
-        <v>373</v>
+        <v>303</v>
       </c>
       <c r="K52" s="51" t="s">
-        <v>342</v>
-      </c>
-      <c r="L52" s="37">
-        <v>2</v>
-      </c>
-      <c r="M52" s="37">
-        <f>L52*5</f>
+        <v>360</v>
+      </c>
+      <c r="L52" s="51">
+        <v>6</v>
+      </c>
+      <c r="M52" s="51">
+        <f t="shared" ref="M52" si="39">L52*5</f>
+        <v>30</v>
+      </c>
+      <c r="N52" s="51">
+        <v>40</v>
+      </c>
+      <c r="O52" s="63" t="s">
+        <v>363</v>
+      </c>
+      <c r="P52" s="52">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="Q52" s="52">
+        <f t="shared" ref="Q52" si="40">P52*N52</f>
+        <v>0.876</v>
+      </c>
+      <c r="R52" s="51"/>
+      <c r="S52" s="59"/>
+    </row>
+    <row r="53" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A53" s="1"/>
+      <c r="B53" s="46">
+        <f>ROW(B53) - ROW($B$9)</f>
+        <v>44</v>
+      </c>
+      <c r="C53" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="D53" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="E53" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="F53" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="G53" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="H53" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="I53" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="J53" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="K53" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="L53" s="37">
+        <v>1</v>
+      </c>
+      <c r="M53" s="37">
+        <f>L53*5</f>
+        <v>5</v>
+      </c>
+      <c r="N53" s="37">
         <v>10</v>
       </c>
-      <c r="N52" s="51">
-        <v>100</v>
-      </c>
-      <c r="O52" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P52" s="52">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="Q52" s="38">
-        <f>P52*N52</f>
-        <v>0.05</v>
-      </c>
-      <c r="R52" s="37"/>
-      <c r="S52" s="59"/>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A53" s="1"/>
-      <c r="B53" s="47">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="C53" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="D53" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="E53" s="51" t="s">
-        <v>131</v>
-      </c>
-      <c r="F53" s="51" t="s">
-        <v>177</v>
-      </c>
-      <c r="G53" s="51" t="s">
-        <v>223</v>
-      </c>
-      <c r="H53" s="51" t="s">
-        <v>247</v>
-      </c>
-      <c r="I53" s="51" t="s">
-        <v>365</v>
-      </c>
-      <c r="J53" s="51" t="s">
-        <v>311</v>
-      </c>
-      <c r="K53" s="51" t="s">
-        <v>343</v>
-      </c>
-      <c r="L53" s="51">
-        <v>6</v>
-      </c>
-      <c r="M53" s="51">
-        <f t="shared" ref="M53" si="42">L53*5</f>
-        <v>30</v>
-      </c>
-      <c r="N53" s="51">
-        <v>100</v>
-      </c>
       <c r="O53" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P53" s="52">
-        <v>8.9999999999999998E-4</v>
-      </c>
-      <c r="Q53" s="52">
-        <f t="shared" ref="Q53" si="43">P53*N53</f>
-        <v>0.09</v>
-      </c>
-      <c r="R53" s="51"/>
+        <v>363</v>
+      </c>
+      <c r="P53" s="38">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="Q53" s="38">
+        <f>P53*N53</f>
+        <v>0.311</v>
+      </c>
+      <c r="R53" s="37"/>
       <c r="S53" s="59"/>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
-      <c r="B54" s="46">
-        <f>ROW(B54) - ROW($B$9)</f>
+      <c r="B54" s="47">
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="C54" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="D54" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="E54" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="F54" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="G54" s="37" t="s">
-        <v>224</v>
-      </c>
-      <c r="H54" s="37" t="s">
-        <v>247</v>
-      </c>
-      <c r="I54" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="J54" s="37" t="s">
-        <v>312</v>
-      </c>
-      <c r="K54" s="37" t="s">
-        <v>344</v>
-      </c>
-      <c r="L54" s="37">
+      <c r="D54" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="E54" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="F54" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="G54" s="51" t="s">
+        <v>217</v>
+      </c>
+      <c r="H54" s="51" t="s">
+        <v>243</v>
+      </c>
+      <c r="I54" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="J54" s="51" t="s">
+        <v>305</v>
+      </c>
+      <c r="K54" s="51" t="s">
+        <v>336</v>
+      </c>
+      <c r="L54" s="51">
         <v>1</v>
       </c>
-      <c r="M54" s="37">
-        <f>L54*5</f>
+      <c r="M54" s="51">
+        <f t="shared" ref="M54" si="41">L54*5</f>
         <v>5</v>
       </c>
-      <c r="N54" s="37">
+      <c r="N54" s="51">
         <v>100</v>
       </c>
       <c r="O54" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P54" s="38">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="Q54" s="38">
-        <f>P54*N54</f>
-        <v>0.06</v>
-      </c>
-      <c r="R54" s="37"/>
+        <v>363</v>
+      </c>
+      <c r="P54" s="52">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q54" s="52">
+        <f t="shared" ref="Q54" si="42">P54*N54</f>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R54" s="51"/>
       <c r="S54" s="59"/>
     </row>
-    <row r="55" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
-      <c r="B55" s="47">
-        <f t="shared" si="0"/>
+      <c r="B55" s="46">
+        <f>ROW(B55) - ROW($B$9)</f>
         <v>46</v>
       </c>
       <c r="C55" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="D55" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="E55" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="F55" s="51" t="s">
-        <v>176</v>
-      </c>
-      <c r="G55" s="51" t="s">
-        <v>225</v>
+      <c r="D55" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="E55" s="37" t="s">
+        <v>127</v>
+      </c>
+      <c r="F55" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="G55" s="64" t="s">
+        <v>218</v>
       </c>
       <c r="H55" s="51" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="I55" s="51" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="J55" s="51" t="s">
-        <v>313</v>
+        <v>368</v>
       </c>
       <c r="K55" s="51" t="s">
-        <v>345</v>
-      </c>
-      <c r="L55" s="51">
-        <v>17</v>
-      </c>
-      <c r="M55" s="51">
-        <f t="shared" ref="M55" si="44">L55*5</f>
-        <v>85</v>
+        <v>337</v>
+      </c>
+      <c r="L55" s="37">
+        <v>2</v>
+      </c>
+      <c r="M55" s="37">
+        <f>L55*5</f>
+        <v>10</v>
       </c>
       <c r="N55" s="51">
         <v>100</v>
       </c>
       <c r="O55" s="63" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="P55" s="52">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="Q55" s="52">
-        <f t="shared" ref="Q55" si="45">P55*N55</f>
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="R55" s="51"/>
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="Q55" s="38">
+        <f>P55*N55</f>
+        <v>0.05</v>
+      </c>
+      <c r="R55" s="37"/>
       <c r="S55" s="59"/>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
-      <c r="B56" s="46">
-        <f>ROW(B56) - ROW($B$9)</f>
+      <c r="B56" s="47">
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="C56" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="D56" s="37" t="s">
-        <v>73</v>
-      </c>
-      <c r="E56" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="F56" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="G56" s="37" t="s">
-        <v>226</v>
-      </c>
-      <c r="H56" s="37" t="s">
-        <v>247</v>
-      </c>
-      <c r="I56" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="J56" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="K56" s="37" t="s">
-        <v>346</v>
-      </c>
-      <c r="L56" s="37">
-        <v>3</v>
-      </c>
-      <c r="M56" s="37">
-        <f>L56*5</f>
-        <v>15</v>
-      </c>
-      <c r="N56" s="37">
+      <c r="D56" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="E56" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="F56" s="51" t="s">
+        <v>174</v>
+      </c>
+      <c r="G56" s="51" t="s">
+        <v>219</v>
+      </c>
+      <c r="H56" s="51" t="s">
+        <v>243</v>
+      </c>
+      <c r="I56" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="J56" s="51" t="s">
+        <v>306</v>
+      </c>
+      <c r="K56" s="51" t="s">
+        <v>338</v>
+      </c>
+      <c r="L56" s="51">
+        <v>6</v>
+      </c>
+      <c r="M56" s="51">
+        <f t="shared" ref="M56" si="43">L56*5</f>
+        <v>30</v>
+      </c>
+      <c r="N56" s="51">
         <v>100</v>
       </c>
       <c r="O56" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P56" s="38">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="Q56" s="38">
-        <f>P56*N56</f>
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="R56" s="37"/>
+        <v>363</v>
+      </c>
+      <c r="P56" s="52">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="Q56" s="52">
+        <f t="shared" ref="Q56" si="44">P56*N56</f>
+        <v>0.09</v>
+      </c>
+      <c r="R56" s="51"/>
       <c r="S56" s="59"/>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
-      <c r="B57" s="47">
-        <f t="shared" si="0"/>
+      <c r="B57" s="46">
+        <f>ROW(B57) - ROW($B$9)</f>
         <v>48</v>
       </c>
       <c r="C57" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="D57" s="51" t="s">
-        <v>74</v>
-      </c>
-      <c r="E57" s="51" t="s">
-        <v>135</v>
-      </c>
-      <c r="F57" s="51" t="s">
-        <v>176</v>
-      </c>
-      <c r="G57" s="51" t="s">
-        <v>227</v>
-      </c>
-      <c r="H57" s="51" t="s">
-        <v>247</v>
-      </c>
-      <c r="I57" s="51" t="s">
-        <v>365</v>
-      </c>
-      <c r="J57" s="51" t="s">
-        <v>315</v>
-      </c>
-      <c r="K57" s="51" t="s">
-        <v>347</v>
-      </c>
-      <c r="L57" s="51">
+      <c r="D57" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E57" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="F57" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="G57" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="H57" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="I57" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="J57" s="37" t="s">
+        <v>307</v>
+      </c>
+      <c r="K57" s="37" t="s">
+        <v>339</v>
+      </c>
+      <c r="L57" s="37">
         <v>1</v>
       </c>
-      <c r="M57" s="51">
-        <f t="shared" ref="M57" si="46">L57*5</f>
+      <c r="M57" s="37">
+        <f>L57*5</f>
         <v>5</v>
       </c>
-      <c r="N57" s="51">
+      <c r="N57" s="37">
         <v>100</v>
       </c>
       <c r="O57" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P57" s="52">
+        <v>363</v>
+      </c>
+      <c r="P57" s="38">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="Q57" s="52">
-        <f t="shared" ref="Q57" si="47">P57*N57</f>
+      <c r="Q57" s="38">
+        <f>P57*N57</f>
         <v>0.06</v>
       </c>
-      <c r="R57" s="51"/>
+      <c r="R57" s="37"/>
       <c r="S57" s="59"/>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
-      <c r="B58" s="46">
-        <f>ROW(B58) - ROW($B$9)</f>
+      <c r="B58" s="47">
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C58" s="53" t="s">
+      <c r="C58" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="D58" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="E58" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="F58" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="G58" s="37" t="s">
-        <v>228</v>
-      </c>
-      <c r="H58" s="37" t="s">
-        <v>247</v>
-      </c>
-      <c r="I58" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="J58" s="37" t="s">
-        <v>316</v>
-      </c>
-      <c r="K58" s="37" t="s">
-        <v>348</v>
-      </c>
-      <c r="L58" s="37">
-        <v>5</v>
-      </c>
-      <c r="M58" s="37">
-        <f>L58*5</f>
-        <v>25</v>
-      </c>
-      <c r="N58" s="37">
+      <c r="D58" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="E58" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="F58" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="G58" s="51" t="s">
+        <v>221</v>
+      </c>
+      <c r="H58" s="51" t="s">
+        <v>243</v>
+      </c>
+      <c r="I58" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="J58" s="51" t="s">
+        <v>308</v>
+      </c>
+      <c r="K58" s="51" t="s">
+        <v>340</v>
+      </c>
+      <c r="L58" s="51">
+        <v>17</v>
+      </c>
+      <c r="M58" s="51">
+        <f t="shared" ref="M58" si="45">L58*5</f>
+        <v>85</v>
+      </c>
+      <c r="N58" s="51">
         <v>100</v>
       </c>
       <c r="O58" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P58" s="38">
+        <v>363</v>
+      </c>
+      <c r="P58" s="52">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="Q58" s="38">
-        <f>P58*N58</f>
+      <c r="Q58" s="52">
+        <f t="shared" ref="Q58" si="46">P58*N58</f>
         <v>6.9999999999999993E-2</v>
       </c>
-      <c r="R58" s="37"/>
+      <c r="R58" s="51"/>
       <c r="S58" s="59"/>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
-      <c r="B59" s="47">
-        <f t="shared" si="0"/>
+      <c r="B59" s="46">
+        <f>ROW(B59) - ROW($B$9)</f>
         <v>50</v>
       </c>
-      <c r="C59" s="53" t="s">
+      <c r="C59" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="D59" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="E59" s="51" t="s">
-        <v>137</v>
-      </c>
-      <c r="F59" s="51" t="s">
-        <v>176</v>
-      </c>
-      <c r="G59" s="64" t="s">
-        <v>229</v>
-      </c>
-      <c r="H59" s="51" t="s">
-        <v>269</v>
-      </c>
-      <c r="I59" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="J59" s="51" t="s">
-        <v>375</v>
-      </c>
-      <c r="K59" s="51" t="s">
-        <v>349</v>
-      </c>
-      <c r="L59" s="51">
-        <v>4</v>
-      </c>
-      <c r="M59" s="51">
-        <f t="shared" ref="M59" si="48">L59*5</f>
-        <v>20</v>
-      </c>
-      <c r="N59" s="51">
+      <c r="D59" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="E59" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="F59" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="G59" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="H59" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="I59" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="J59" s="37" t="s">
+        <v>309</v>
+      </c>
+      <c r="K59" s="37" t="s">
+        <v>341</v>
+      </c>
+      <c r="L59" s="37">
+        <v>3</v>
+      </c>
+      <c r="M59" s="37">
+        <f>L59*5</f>
+        <v>15</v>
+      </c>
+      <c r="N59" s="37">
         <v>100</v>
       </c>
       <c r="O59" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P59" s="52">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="Q59" s="52">
-        <f t="shared" ref="Q59" si="49">P59*N59</f>
-        <v>0.04</v>
-      </c>
-      <c r="R59" s="51"/>
+        <v>363</v>
+      </c>
+      <c r="P59" s="38">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q59" s="38">
+        <f>P59*N59</f>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R59" s="37"/>
       <c r="S59" s="59"/>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
-      <c r="B60" s="46">
-        <f>ROW(B60) - ROW($B$9)</f>
+      <c r="B60" s="47">
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C60" s="53" t="s">
+      <c r="C60" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="D60" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="E60" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="F60" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="G60" s="37" t="s">
-        <v>230</v>
-      </c>
-      <c r="H60" s="37" t="s">
-        <v>247</v>
-      </c>
-      <c r="I60" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="J60" s="37" t="s">
-        <v>317</v>
-      </c>
-      <c r="K60" s="37" t="s">
-        <v>350</v>
-      </c>
-      <c r="L60" s="37">
-        <v>2</v>
-      </c>
-      <c r="M60" s="37">
-        <f>L60*5</f>
-        <v>10</v>
-      </c>
-      <c r="N60" s="37">
+      <c r="D60" s="51" t="s">
+        <v>72</v>
+      </c>
+      <c r="E60" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="F60" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="G60" s="51" t="s">
+        <v>223</v>
+      </c>
+      <c r="H60" s="51" t="s">
+        <v>243</v>
+      </c>
+      <c r="I60" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="J60" s="51" t="s">
+        <v>310</v>
+      </c>
+      <c r="K60" s="51" t="s">
+        <v>342</v>
+      </c>
+      <c r="L60" s="51">
+        <v>1</v>
+      </c>
+      <c r="M60" s="51">
+        <f t="shared" ref="M60" si="47">L60*5</f>
+        <v>5</v>
+      </c>
+      <c r="N60" s="51">
         <v>100</v>
       </c>
       <c r="O60" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P60" s="38">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q60" s="38">
-        <f>P60*N60</f>
-        <v>0.13</v>
-      </c>
-      <c r="R60" s="37"/>
+        <v>363</v>
+      </c>
+      <c r="P60" s="52">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="Q60" s="52">
+        <f t="shared" ref="Q60" si="48">P60*N60</f>
+        <v>0.06</v>
+      </c>
+      <c r="R60" s="51"/>
       <c r="S60" s="59"/>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
-      <c r="B61" s="47">
+      <c r="B61" s="46">
+        <f>ROW(B61) - ROW($B$9)</f>
+        <v>52</v>
+      </c>
+      <c r="C61" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="D61" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="E61" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="F61" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="G61" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="H61" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="I61" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="J61" s="37" t="s">
+        <v>311</v>
+      </c>
+      <c r="K61" s="37" t="s">
+        <v>343</v>
+      </c>
+      <c r="L61" s="37">
+        <v>5</v>
+      </c>
+      <c r="M61" s="37">
+        <f>L61*5</f>
+        <v>25</v>
+      </c>
+      <c r="N61" s="37">
+        <v>100</v>
+      </c>
+      <c r="O61" s="63" t="s">
+        <v>363</v>
+      </c>
+      <c r="P61" s="38">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q61" s="38">
+        <f>P61*N61</f>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R61" s="37"/>
+      <c r="S61" s="59"/>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A62" s="1"/>
+      <c r="B62" s="47">
         <f t="shared" si="0"/>
-        <v>52</v>
-      </c>
-      <c r="C61" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="C62" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="D61" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="E61" s="51" t="s">
-        <v>139</v>
-      </c>
-      <c r="F61" s="51" t="s">
-        <v>366</v>
-      </c>
-      <c r="G61" s="51" t="s">
-        <v>231</v>
-      </c>
-      <c r="H61" s="51" t="s">
-        <v>247</v>
-      </c>
-      <c r="I61" s="51" t="s">
-        <v>365</v>
-      </c>
-      <c r="J61" s="51" t="s">
-        <v>318</v>
-      </c>
-      <c r="K61" s="51" t="s">
-        <v>351</v>
-      </c>
-      <c r="L61" s="51">
-        <v>2</v>
-      </c>
-      <c r="M61" s="51">
-        <f t="shared" ref="M61" si="50">L61*5</f>
-        <v>10</v>
-      </c>
-      <c r="N61" s="51">
+      <c r="D62" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="E62" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="F62" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="G62" s="64" t="s">
+        <v>225</v>
+      </c>
+      <c r="H62" s="51" t="s">
+        <v>264</v>
+      </c>
+      <c r="I62" s="51" t="s">
+        <v>369</v>
+      </c>
+      <c r="J62" s="51" t="s">
+        <v>370</v>
+      </c>
+      <c r="K62" s="51" t="s">
+        <v>344</v>
+      </c>
+      <c r="L62" s="51">
+        <v>4</v>
+      </c>
+      <c r="M62" s="51">
+        <f t="shared" ref="M62" si="49">L62*5</f>
+        <v>20</v>
+      </c>
+      <c r="N62" s="51">
         <v>100</v>
       </c>
-      <c r="O61" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P61" s="52">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="Q61" s="52">
-        <f t="shared" ref="Q61" si="51">P61*N61</f>
-        <v>0.69</v>
-      </c>
-      <c r="R61" s="51"/>
-      <c r="S61" s="59"/>
-    </row>
-    <row r="62" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A62" s="1"/>
-      <c r="B62" s="46">
-        <f>ROW(B62) - ROW($B$9)</f>
-        <v>53</v>
-      </c>
-      <c r="C62" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="D62" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="E62" s="37" t="s">
-        <v>140</v>
-      </c>
-      <c r="F62" s="37" t="s">
-        <v>366</v>
-      </c>
-      <c r="G62" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="H62" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="I62" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="J62" s="37" t="s">
-        <v>379</v>
-      </c>
-      <c r="K62" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="L62" s="37">
-        <v>1</v>
-      </c>
-      <c r="M62" s="37">
-        <f>L62*5</f>
-        <v>5</v>
-      </c>
-      <c r="N62" s="37">
-        <v>10</v>
-      </c>
       <c r="O62" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P62" s="38">
-        <v>0.12659999999999999</v>
-      </c>
-      <c r="Q62" s="38">
-        <f>P62*N62</f>
-        <v>1.266</v>
-      </c>
-      <c r="R62" s="37"/>
+        <v>363</v>
+      </c>
+      <c r="P62" s="52">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="Q62" s="52">
+        <f t="shared" ref="Q62" si="50">P62*N62</f>
+        <v>0.04</v>
+      </c>
+      <c r="R62" s="51"/>
       <c r="S62" s="59"/>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
-      <c r="B63" s="47">
-        <f t="shared" si="0"/>
+      <c r="B63" s="46">
+        <f>ROW(B63) - ROW($B$9)</f>
         <v>54</v>
       </c>
-      <c r="C63" s="54" t="s">
-        <v>24</v>
-      </c>
-      <c r="D63" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="E63" s="51" t="s">
-        <v>141</v>
-      </c>
-      <c r="F63" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="G63" s="51" t="s">
-        <v>232</v>
-      </c>
-      <c r="H63" s="51" t="s">
-        <v>249</v>
-      </c>
-      <c r="I63" s="51" t="s">
-        <v>365</v>
-      </c>
-      <c r="J63" s="51" t="s">
-        <v>319</v>
-      </c>
-      <c r="K63" s="51" t="s">
-        <v>365</v>
-      </c>
-      <c r="L63" s="51">
-        <v>1</v>
-      </c>
-      <c r="M63" s="51">
-        <f t="shared" ref="M63" si="52">L63*5</f>
-        <v>5</v>
-      </c>
-      <c r="N63" s="51">
-        <v>6</v>
+      <c r="C63" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="D63" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="E63" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="F63" s="37" t="s">
+        <v>175</v>
+      </c>
+      <c r="G63" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="H63" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="I63" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="J63" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="K63" s="37" t="s">
+        <v>345</v>
+      </c>
+      <c r="L63" s="37">
+        <v>2</v>
+      </c>
+      <c r="M63" s="37">
+        <f>L63*5</f>
+        <v>10</v>
+      </c>
+      <c r="N63" s="37">
+        <v>100</v>
       </c>
       <c r="O63" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P63" s="52">
-        <v>0.35320000000000001</v>
-      </c>
-      <c r="Q63" s="52">
-        <f t="shared" ref="Q63" si="53">P63*N63</f>
-        <v>2.1192000000000002</v>
-      </c>
-      <c r="R63" s="51"/>
+        <v>363</v>
+      </c>
+      <c r="P63" s="38">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q63" s="38">
+        <f>P63*N63</f>
+        <v>0.13</v>
+      </c>
+      <c r="R63" s="37"/>
       <c r="S63" s="59"/>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
-      <c r="B64" s="46">
-        <f>ROW(B64) - ROW($B$9)</f>
+      <c r="B64" s="47">
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C64" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="D64" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="E64" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="F64" s="37" t="s">
-        <v>181</v>
-      </c>
-      <c r="G64" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="H64" s="37" t="s">
-        <v>249</v>
-      </c>
-      <c r="I64" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="J64" s="37" t="s">
-        <v>320</v>
-      </c>
-      <c r="K64" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="L64" s="37">
+      <c r="C64" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="D64" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="E64" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="F64" s="51" t="s">
+        <v>361</v>
+      </c>
+      <c r="G64" s="51" t="s">
+        <v>227</v>
+      </c>
+      <c r="H64" s="51" t="s">
+        <v>243</v>
+      </c>
+      <c r="I64" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="J64" s="51" t="s">
+        <v>313</v>
+      </c>
+      <c r="K64" s="51" t="s">
+        <v>346</v>
+      </c>
+      <c r="L64" s="51">
+        <v>2</v>
+      </c>
+      <c r="M64" s="51">
+        <f t="shared" ref="M64" si="51">L64*5</f>
+        <v>10</v>
+      </c>
+      <c r="N64" s="51">
+        <v>100</v>
+      </c>
+      <c r="O64" s="63" t="s">
+        <v>363</v>
+      </c>
+      <c r="P64" s="52">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="Q64" s="52">
+        <f t="shared" ref="Q64" si="52">P64*N64</f>
+        <v>0.69</v>
+      </c>
+      <c r="R64" s="51"/>
+      <c r="S64" s="59"/>
+    </row>
+    <row r="65" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A65" s="1"/>
+      <c r="B65" s="46">
+        <f>ROW(B65) - ROW($B$9)</f>
+        <v>56</v>
+      </c>
+      <c r="C65" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="D65" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="E65" s="37" t="s">
+        <v>137</v>
+      </c>
+      <c r="F65" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="G65" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="H65" s="37" t="s">
+        <v>265</v>
+      </c>
+      <c r="I65" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="J65" s="37" t="s">
+        <v>373</v>
+      </c>
+      <c r="K65" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="L65" s="37">
         <v>1</v>
       </c>
-      <c r="M64" s="37">
-        <f>L64*5</f>
+      <c r="M65" s="37">
+        <f>L65*5</f>
         <v>5</v>
       </c>
-      <c r="N64" s="37">
-        <v>6</v>
-      </c>
-      <c r="O64" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P64" s="38">
-        <v>0.46460000000000001</v>
-      </c>
-      <c r="Q64" s="38">
-        <f>P64*N64</f>
-        <v>2.7876000000000003</v>
-      </c>
-      <c r="R64" s="37"/>
-      <c r="S64" s="59"/>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A65" s="1"/>
-      <c r="B65" s="47">
-        <f t="shared" si="0"/>
-        <v>56</v>
-      </c>
-      <c r="C65" s="54" t="s">
-        <v>24</v>
-      </c>
-      <c r="D65" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="E65" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="F65" s="51" t="s">
-        <v>182</v>
-      </c>
-      <c r="G65" s="51" t="s">
-        <v>234</v>
-      </c>
-      <c r="H65" s="51" t="s">
-        <v>271</v>
-      </c>
-      <c r="I65" s="51" t="s">
-        <v>365</v>
-      </c>
-      <c r="J65" s="51" t="s">
-        <v>321</v>
-      </c>
-      <c r="K65" s="51" t="s">
-        <v>365</v>
-      </c>
-      <c r="L65" s="51">
-        <v>1</v>
-      </c>
-      <c r="M65" s="51">
-        <f t="shared" ref="M65" si="54">L65*5</f>
-        <v>5</v>
-      </c>
-      <c r="N65" s="51">
-        <v>6</v>
+      <c r="N65" s="37">
+        <v>10</v>
       </c>
       <c r="O65" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P65" s="52">
-        <v>0.37230000000000002</v>
-      </c>
-      <c r="Q65" s="52">
-        <f t="shared" ref="Q65" si="55">P65*N65</f>
-        <v>2.2338</v>
-      </c>
-      <c r="R65" s="51"/>
+        <v>363</v>
+      </c>
+      <c r="P65" s="38">
+        <v>0.12659999999999999</v>
+      </c>
+      <c r="Q65" s="38">
+        <f>P65*N65</f>
+        <v>1.266</v>
+      </c>
+      <c r="R65" s="37"/>
       <c r="S65" s="59"/>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
-      <c r="B66" s="46">
-        <f>ROW(B66) - ROW($B$9)</f>
+      <c r="B66" s="47">
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="C66" s="53" t="s">
+      <c r="C66" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="D66" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="E66" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="F66" s="37" t="s">
-        <v>183</v>
-      </c>
-      <c r="G66" s="37" t="s">
-        <v>235</v>
-      </c>
-      <c r="H66" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="I66" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="J66" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="K66" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="L66" s="37">
+      <c r="D66" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="E66" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="F66" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="G66" s="51" t="s">
+        <v>228</v>
+      </c>
+      <c r="H66" s="51" t="s">
+        <v>245</v>
+      </c>
+      <c r="I66" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="J66" s="51" t="s">
+        <v>314</v>
+      </c>
+      <c r="K66" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="L66" s="51">
         <v>1</v>
       </c>
-      <c r="M66" s="37">
-        <f>L66*5</f>
+      <c r="M66" s="51">
+        <f t="shared" ref="M66" si="53">L66*5</f>
         <v>5</v>
       </c>
-      <c r="N66" s="37">
+      <c r="N66" s="51">
         <v>6</v>
       </c>
       <c r="O66" s="63" t="s">
-        <v>367</v>
-      </c>
-      <c r="P66" s="38">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="Q66" s="38">
-        <f>P66*N66</f>
-        <v>15.059999999999999</v>
-      </c>
-      <c r="R66" s="37"/>
+        <v>363</v>
+      </c>
+      <c r="P66" s="52">
+        <v>0.35320000000000001</v>
+      </c>
+      <c r="Q66" s="52">
+        <f t="shared" ref="Q66" si="54">P66*N66</f>
+        <v>2.1192000000000002</v>
+      </c>
+      <c r="R66" s="51"/>
       <c r="S66" s="59"/>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
-      <c r="B67" s="47">
+      <c r="B67" s="46">
+        <f>ROW(B67) - ROW($B$9)</f>
+        <v>58</v>
+      </c>
+      <c r="C67" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D67" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="E67" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="F67" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="G67" s="37" t="s">
+        <v>229</v>
+      </c>
+      <c r="H67" s="37" t="s">
+        <v>245</v>
+      </c>
+      <c r="I67" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="J67" s="37" t="s">
+        <v>315</v>
+      </c>
+      <c r="K67" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="L67" s="37">
+        <v>1</v>
+      </c>
+      <c r="M67" s="37">
+        <f>L67*5</f>
+        <v>5</v>
+      </c>
+      <c r="N67" s="37">
+        <v>6</v>
+      </c>
+      <c r="O67" s="63" t="s">
+        <v>363</v>
+      </c>
+      <c r="P67" s="38">
+        <v>0.46460000000000001</v>
+      </c>
+      <c r="Q67" s="38">
+        <f>P67*N67</f>
+        <v>2.7876000000000003</v>
+      </c>
+      <c r="R67" s="37"/>
+      <c r="S67" s="59"/>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A68" s="1"/>
+      <c r="B68" s="47">
         <f t="shared" si="0"/>
-        <v>58</v>
-      </c>
-      <c r="C67" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="C68" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="D67" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="E67" s="51" t="s">
-        <v>145</v>
-      </c>
-      <c r="F67" s="51" t="s">
-        <v>184</v>
-      </c>
-      <c r="G67" s="51" t="s">
-        <v>236</v>
-      </c>
-      <c r="H67" s="51" t="s">
-        <v>273</v>
-      </c>
-      <c r="I67" s="51"/>
-      <c r="J67" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="K67" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="L67" s="51">
+      <c r="D68" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="E68" s="51" t="s">
+        <v>140</v>
+      </c>
+      <c r="F68" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="G68" s="51" t="s">
+        <v>230</v>
+      </c>
+      <c r="H68" s="51" t="s">
+        <v>266</v>
+      </c>
+      <c r="I68" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="J68" s="51" t="s">
+        <v>316</v>
+      </c>
+      <c r="K68" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="L68" s="51">
         <v>1</v>
       </c>
-      <c r="M67" s="51">
-        <f t="shared" ref="M67" si="56">L67*5</f>
-        <v>5</v>
-      </c>
-      <c r="N67" s="51">
-        <v>6</v>
-      </c>
-      <c r="O67" s="63" t="s">
-        <v>368</v>
-      </c>
-      <c r="P67" s="52">
-        <v>1.8821000000000001</v>
-      </c>
-      <c r="Q67" s="52">
-        <f t="shared" ref="Q67" si="57">P67*N67</f>
-        <v>11.2926</v>
-      </c>
-      <c r="R67" s="51"/>
-      <c r="S67" s="59"/>
-    </row>
-    <row r="68" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A68" s="1"/>
-      <c r="B68" s="46">
-        <f>ROW(B68) - ROW($B$9)</f>
-        <v>59</v>
-      </c>
-      <c r="C68" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="D68" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="E68" s="37" t="s">
-        <v>146</v>
-      </c>
-      <c r="F68" s="37" t="s">
-        <v>366</v>
-      </c>
-      <c r="G68" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="H68" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="I68" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="J68" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="K68" s="51" t="s">
-        <v>365</v>
-      </c>
-      <c r="L68" s="37">
-        <v>1</v>
-      </c>
-      <c r="M68" s="37">
-        <f>L68*5</f>
+      <c r="M68" s="51">
+        <f t="shared" ref="M68" si="55">L68*5</f>
         <v>5</v>
       </c>
       <c r="N68" s="51">
         <v>6</v>
       </c>
-      <c r="O68" s="60" t="s">
-        <v>369</v>
+      <c r="O68" s="63" t="s">
+        <v>363</v>
       </c>
       <c r="P68" s="52">
-        <v>27.036000000000001</v>
-      </c>
-      <c r="Q68" s="38">
-        <f>P68*N68</f>
-        <v>162.21600000000001</v>
-      </c>
-      <c r="R68" s="37"/>
+        <v>0.37230000000000002</v>
+      </c>
+      <c r="Q68" s="52">
+        <f t="shared" ref="Q68" si="56">P68*N68</f>
+        <v>2.2338</v>
+      </c>
+      <c r="R68" s="51"/>
       <c r="S68" s="59"/>
     </row>
-    <row r="69" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
-      <c r="B69" s="47">
-        <f t="shared" si="0"/>
+      <c r="B69" s="46">
+        <f>ROW(B69) - ROW($B$9)</f>
         <v>60</v>
       </c>
-      <c r="C69" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="D69" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="E69" s="51" t="s">
-        <v>147</v>
-      </c>
-      <c r="F69" s="51" t="s">
-        <v>164</v>
-      </c>
-      <c r="G69" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="H69" s="51" t="s">
-        <v>275</v>
-      </c>
-      <c r="I69" s="51" t="s">
-        <v>365</v>
-      </c>
-      <c r="J69" s="51" t="s">
-        <v>323</v>
+      <c r="C69" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D69" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="E69" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="F69" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="G69" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="H69" s="37" t="s">
+        <v>267</v>
+      </c>
+      <c r="I69" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="J69" s="37" t="s">
+        <v>360</v>
       </c>
       <c r="K69" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="L69" s="51">
+        <v>360</v>
+      </c>
+      <c r="L69" s="37">
         <v>1</v>
       </c>
-      <c r="M69" s="51">
-        <f t="shared" ref="M69" si="58">L69*5</f>
+      <c r="M69" s="37">
+        <f>L69*5</f>
         <v>5</v>
       </c>
       <c r="N69" s="37">
-        <v>20</v>
-      </c>
-      <c r="O69" s="60" t="s">
-        <v>368</v>
+        <v>6</v>
+      </c>
+      <c r="O69" s="63" t="s">
+        <v>362</v>
       </c>
       <c r="P69" s="38">
-        <v>3.85E-2</v>
-      </c>
-      <c r="Q69" s="52">
-        <f t="shared" ref="Q69" si="59">P69*N69</f>
-        <v>0.77</v>
-      </c>
-      <c r="R69" s="51"/>
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="Q69" s="38">
+        <f>P69*N69</f>
+        <v>15.059999999999999</v>
+      </c>
+      <c r="R69" s="37"/>
       <c r="S69" s="59"/>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
-      <c r="B70" s="46">
-        <f>ROW(B70) - ROW($B$9)</f>
+      <c r="B70" s="47">
+        <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="C70" s="53" t="s">
+      <c r="C70" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="D70" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="E70" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="F70" s="37" t="s">
-        <v>186</v>
-      </c>
-      <c r="G70" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="H70" s="37" t="s">
-        <v>276</v>
-      </c>
-      <c r="I70" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="J70" s="37" t="s">
-        <v>324</v>
-      </c>
-      <c r="K70" s="51" t="s">
-        <v>365</v>
-      </c>
-      <c r="L70" s="37">
+      <c r="D70" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="E70" s="51" t="s">
+        <v>142</v>
+      </c>
+      <c r="F70" s="51" t="s">
+        <v>181</v>
+      </c>
+      <c r="G70" s="51" t="s">
+        <v>232</v>
+      </c>
+      <c r="H70" s="51" t="s">
+        <v>268</v>
+      </c>
+      <c r="I70" s="51"/>
+      <c r="J70" s="51" t="s">
+        <v>317</v>
+      </c>
+      <c r="K70" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="L70" s="51">
         <v>1</v>
       </c>
-      <c r="M70" s="37">
-        <f>L70*5</f>
+      <c r="M70" s="51">
+        <f t="shared" ref="M70" si="57">L70*5</f>
         <v>5</v>
       </c>
       <c r="N70" s="51">
         <v>6</v>
       </c>
-      <c r="O70" s="60" t="s">
-        <v>368</v>
+      <c r="O70" s="63" t="s">
+        <v>363</v>
       </c>
       <c r="P70" s="52">
-        <v>0.43280000000000002</v>
-      </c>
-      <c r="Q70" s="38">
-        <f>P70*N70</f>
-        <v>2.5968</v>
-      </c>
-      <c r="R70" s="37"/>
+        <v>1.8821000000000001</v>
+      </c>
+      <c r="Q70" s="52">
+        <f t="shared" ref="Q70" si="58">P70*N70</f>
+        <v>11.2926</v>
+      </c>
+      <c r="R70" s="51"/>
       <c r="S70" s="59"/>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
-      <c r="B71" s="47">
-        <f t="shared" si="0"/>
+      <c r="B71" s="46">
+        <f>ROW(B71) - ROW($B$9)</f>
         <v>62</v>
       </c>
-      <c r="C71" s="54" t="s">
+      <c r="C71" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="D71" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="E71" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="F71" s="51" t="s">
-        <v>187</v>
-      </c>
-      <c r="G71" s="51" t="s">
-        <v>239</v>
-      </c>
-      <c r="H71" s="51" t="s">
-        <v>276</v>
-      </c>
-      <c r="I71" s="51" t="s">
-        <v>365</v>
-      </c>
-      <c r="J71" s="51" t="s">
-        <v>325</v>
-      </c>
-      <c r="K71" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="L71" s="51">
+      <c r="D71" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="E71" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="F71" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="G71" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="H71" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="I71" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="J71" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="K71" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="L71" s="37">
         <v>1</v>
       </c>
-      <c r="M71" s="51">
-        <f t="shared" ref="M71" si="60">L71*5</f>
+      <c r="M71" s="37">
+        <f>L71*5</f>
         <v>5</v>
       </c>
       <c r="N71" s="51">
         <v>6</v>
       </c>
-      <c r="O71" s="63" t="s">
-        <v>368</v>
+      <c r="O71" s="60" t="s">
+        <v>364</v>
       </c>
       <c r="P71" s="52">
+        <v>27.036000000000001</v>
+      </c>
+      <c r="Q71" s="38">
+        <f>P71*N71</f>
+        <v>162.21600000000001</v>
+      </c>
+      <c r="R71" s="37"/>
+      <c r="S71" s="59"/>
+    </row>
+    <row r="72" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A72" s="1"/>
+      <c r="B72" s="47">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="C72" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="E72" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="F72" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="G72" s="51" t="s">
+        <v>233</v>
+      </c>
+      <c r="H72" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="I72" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="J72" s="51" t="s">
+        <v>318</v>
+      </c>
+      <c r="K72" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="L72" s="51">
+        <v>1</v>
+      </c>
+      <c r="M72" s="51">
+        <f t="shared" ref="M72" si="59">L72*5</f>
+        <v>5</v>
+      </c>
+      <c r="N72" s="37">
+        <v>20</v>
+      </c>
+      <c r="O72" s="60" t="s">
+        <v>363</v>
+      </c>
+      <c r="P72" s="38">
+        <v>3.85E-2</v>
+      </c>
+      <c r="Q72" s="52">
+        <f t="shared" ref="Q72" si="60">P72*N72</f>
+        <v>0.77</v>
+      </c>
+      <c r="R72" s="51"/>
+      <c r="S72" s="59"/>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A73" s="1"/>
+      <c r="B73" s="46">
+        <f>ROW(B73) - ROW($B$9)</f>
+        <v>64</v>
+      </c>
+      <c r="C73" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D73" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="E73" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="F73" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="G73" s="37" t="s">
+        <v>234</v>
+      </c>
+      <c r="H73" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="I73" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="J73" s="37" t="s">
+        <v>319</v>
+      </c>
+      <c r="K73" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="L73" s="37">
+        <v>1</v>
+      </c>
+      <c r="M73" s="37">
+        <f>L73*5</f>
+        <v>5</v>
+      </c>
+      <c r="N73" s="51">
+        <v>6</v>
+      </c>
+      <c r="O73" s="60" t="s">
+        <v>363</v>
+      </c>
+      <c r="P73" s="52">
+        <v>0.43280000000000002</v>
+      </c>
+      <c r="Q73" s="38">
+        <f>P73*N73</f>
+        <v>2.5968</v>
+      </c>
+      <c r="R73" s="37"/>
+      <c r="S73" s="59"/>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A74" s="1"/>
+      <c r="B74" s="47">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="C74" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="D74" s="51" t="s">
+        <v>86</v>
+      </c>
+      <c r="E74" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="F74" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="G74" s="51" t="s">
+        <v>235</v>
+      </c>
+      <c r="H74" s="51" t="s">
+        <v>271</v>
+      </c>
+      <c r="I74" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="J74" s="51" t="s">
+        <v>320</v>
+      </c>
+      <c r="K74" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="L74" s="51">
+        <v>1</v>
+      </c>
+      <c r="M74" s="51">
+        <f t="shared" ref="M74" si="61">L74*5</f>
+        <v>5</v>
+      </c>
+      <c r="N74" s="51">
+        <v>6</v>
+      </c>
+      <c r="O74" s="63" t="s">
+        <v>363</v>
+      </c>
+      <c r="P74" s="52">
         <v>0.80659999999999998</v>
       </c>
-      <c r="Q71" s="52">
-        <f t="shared" ref="Q71" si="61">P71*N71</f>
+      <c r="Q74" s="52">
+        <f t="shared" ref="Q74" si="62">P74*N74</f>
         <v>4.8395999999999999</v>
       </c>
-      <c r="R71" s="51"/>
-      <c r="S71" s="59"/>
-    </row>
-    <row r="72" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="1"/>
-      <c r="B72" s="46">
-        <f>ROW(B72) - ROW($B$9)</f>
-        <v>63</v>
-      </c>
-      <c r="C72" s="53" t="s">
+      <c r="R74" s="51"/>
+      <c r="S74" s="59"/>
+    </row>
+    <row r="75" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="1"/>
+      <c r="B75" s="46">
+        <f>ROW(B75) - ROW($B$9)</f>
+        <v>66</v>
+      </c>
+      <c r="C75" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="D72" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E72" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="F72" s="37" t="s">
-        <v>366</v>
-      </c>
-      <c r="G72" s="37" t="s">
-        <v>240</v>
-      </c>
-      <c r="H72" s="37" t="s">
-        <v>277</v>
-      </c>
-      <c r="I72" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="J72" s="37" t="s">
-        <v>326</v>
-      </c>
-      <c r="K72" s="37" t="s">
-        <v>352</v>
-      </c>
-      <c r="L72" s="37">
+      <c r="D75" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="E75" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="F75" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="G75" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="H75" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="I75" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="J75" s="37" t="s">
+        <v>321</v>
+      </c>
+      <c r="K75" s="37" t="s">
+        <v>347</v>
+      </c>
+      <c r="L75" s="37">
         <v>1</v>
       </c>
-      <c r="M72" s="37">
-        <f>L72*5</f>
+      <c r="M75" s="37">
+        <f>L75*5</f>
         <v>5</v>
       </c>
-      <c r="N72" s="37">
+      <c r="N75" s="37">
         <v>10</v>
       </c>
-      <c r="O72" s="60" t="s">
-        <v>368</v>
-      </c>
-      <c r="P72" s="38">
+      <c r="O75" s="60" t="s">
+        <v>363</v>
+      </c>
+      <c r="P75" s="38">
         <v>0.08</v>
       </c>
-      <c r="Q72" s="38">
-        <f>P72*N72</f>
+      <c r="Q75" s="38">
+        <f>P75*N75</f>
         <v>0.8</v>
       </c>
-      <c r="R72" s="37"/>
-      <c r="S72" s="39"/>
-    </row>
-    <row r="73" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="1"/>
-      <c r="B73" s="40"/>
-      <c r="C73" s="41"/>
-      <c r="D73" s="42"/>
-      <c r="E73" s="43"/>
-      <c r="F73" s="44"/>
-      <c r="G73" s="45"/>
-      <c r="H73" s="44"/>
-      <c r="I73" s="45"/>
-      <c r="J73" s="44"/>
-      <c r="K73" s="45"/>
-      <c r="L73" s="45"/>
-      <c r="M73" s="45"/>
-      <c r="N73" s="87" t="s">
+      <c r="R75" s="37"/>
+      <c r="S75" s="39"/>
+    </row>
+    <row r="76" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="1"/>
+      <c r="B76" s="89">
+        <v>67</v>
+      </c>
+      <c r="C76" s="54" t="s">
+        <v>406</v>
+      </c>
+      <c r="D76" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="E76" s="51" t="s">
+        <v>407</v>
+      </c>
+      <c r="F76" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="G76" s="51" t="s">
+        <v>408</v>
+      </c>
+      <c r="H76" s="51" t="s">
+        <v>409</v>
+      </c>
+      <c r="I76" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="J76" s="51" t="s">
+        <v>410</v>
+      </c>
+      <c r="K76" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="L76" s="51">
+        <v>1</v>
+      </c>
+      <c r="M76" s="51">
+        <f>L76*5</f>
         <v>5</v>
       </c>
-      <c r="O73" s="88"/>
-      <c r="P73" s="88"/>
-      <c r="Q73" s="48">
-        <f>SUM(Q10:Q72)</f>
-        <v>268.65120000000002</v>
-      </c>
-      <c r="R73" s="83"/>
-      <c r="S73" s="84"/>
-    </row>
-    <row r="74" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="1"/>
-      <c r="B74" s="25"/>
-      <c r="C74" s="36"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="10"/>
-      <c r="F74" s="10"/>
-      <c r="G74" s="10"/>
-      <c r="H74" s="10"/>
-      <c r="I74" s="10"/>
-      <c r="J74" s="10"/>
-      <c r="K74" s="10"/>
-      <c r="L74" s="10"/>
-      <c r="M74" s="10"/>
-      <c r="N74" s="87" t="s">
+      <c r="N76" s="51">
         <v>6</v>
       </c>
-      <c r="O74" s="88"/>
-      <c r="P74" s="88"/>
-      <c r="Q74" s="49">
-        <f>Q73/5</f>
-        <v>53.730240000000002</v>
-      </c>
-      <c r="R74" s="85"/>
-      <c r="S74" s="86"/>
+      <c r="O76" s="63" t="s">
+        <v>363</v>
+      </c>
+      <c r="P76" s="52">
+        <v>1.1121000000000001</v>
+      </c>
+      <c r="Q76" s="52">
+        <f>P76*N76</f>
+        <v>6.672600000000001</v>
+      </c>
+      <c r="R76" s="51"/>
+      <c r="S76" s="59"/>
+    </row>
+    <row r="77" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="1"/>
+      <c r="B77" s="40"/>
+      <c r="C77" s="41"/>
+      <c r="D77" s="42"/>
+      <c r="E77" s="43"/>
+      <c r="F77" s="44"/>
+      <c r="G77" s="45"/>
+      <c r="H77" s="44"/>
+      <c r="I77" s="45"/>
+      <c r="J77" s="44"/>
+      <c r="K77" s="45"/>
+      <c r="L77" s="45"/>
+      <c r="M77" s="45"/>
+      <c r="N77" s="87" t="s">
+        <v>5</v>
+      </c>
+      <c r="O77" s="88"/>
+      <c r="P77" s="88"/>
+      <c r="Q77" s="48">
+        <f>SUM(Q10:Q76)</f>
+        <v>276.32780000000002</v>
+      </c>
+      <c r="R77" s="83"/>
+      <c r="S77" s="84"/>
+    </row>
+    <row r="78" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="1"/>
+      <c r="B78" s="25"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="10"/>
+      <c r="F78" s="10"/>
+      <c r="G78" s="10"/>
+      <c r="H78" s="10"/>
+      <c r="I78" s="10"/>
+      <c r="J78" s="10"/>
+      <c r="K78" s="10"/>
+      <c r="L78" s="10"/>
+      <c r="M78" s="10"/>
+      <c r="N78" s="87" t="s">
+        <v>6</v>
+      </c>
+      <c r="O78" s="88"/>
+      <c r="P78" s="88"/>
+      <c r="Q78" s="49">
+        <f>Q77/5</f>
+        <v>55.265560000000008</v>
+      </c>
+      <c r="R78" s="85"/>
+      <c r="S78" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R73:S74"/>
-    <mergeCell ref="N73:P73"/>
-    <mergeCell ref="N74:P74"/>
+    <mergeCell ref="R77:S78"/>
+    <mergeCell ref="N77:P77"/>
+    <mergeCell ref="N78:P78"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O18" r:id="rId1"/>
     <hyperlink ref="O22" r:id="rId2"/>
-    <hyperlink ref="O40" r:id="rId3" display="LCSC"/>
-    <hyperlink ref="O68" r:id="rId4"/>
-    <hyperlink ref="O69" r:id="rId5"/>
-    <hyperlink ref="O70" r:id="rId6"/>
+    <hyperlink ref="O42" r:id="rId3" display="LCSC"/>
+    <hyperlink ref="O71" r:id="rId4"/>
+    <hyperlink ref="O72" r:id="rId5"/>
+    <hyperlink ref="O73" r:id="rId6"/>
     <hyperlink ref="O12" r:id="rId7"/>
     <hyperlink ref="O13" r:id="rId8"/>
     <hyperlink ref="O16" r:id="rId9"/>
-    <hyperlink ref="O58" r:id="rId10"/>
-    <hyperlink ref="O52" r:id="rId11"/>
-    <hyperlink ref="O54" r:id="rId12"/>
-    <hyperlink ref="O53" r:id="rId13"/>
-    <hyperlink ref="O55" r:id="rId14"/>
-    <hyperlink ref="O56" r:id="rId15"/>
-    <hyperlink ref="O59" r:id="rId16"/>
-    <hyperlink ref="O36" r:id="rId17"/>
-    <hyperlink ref="O34" r:id="rId18"/>
-    <hyperlink ref="O31" r:id="rId19"/>
-    <hyperlink ref="O30" r:id="rId20"/>
-    <hyperlink ref="O37" r:id="rId21"/>
-    <hyperlink ref="O38" r:id="rId22"/>
-    <hyperlink ref="O42" r:id="rId23"/>
-    <hyperlink ref="O45" r:id="rId24"/>
-    <hyperlink ref="O46" r:id="rId25"/>
-    <hyperlink ref="O23" r:id="rId26"/>
-    <hyperlink ref="O14" r:id="rId27"/>
-    <hyperlink ref="O15" r:id="rId28"/>
-    <hyperlink ref="O17" r:id="rId29"/>
-    <hyperlink ref="O19" r:id="rId30"/>
-    <hyperlink ref="O20" r:id="rId31"/>
-    <hyperlink ref="O21" r:id="rId32"/>
-    <hyperlink ref="O24" r:id="rId33"/>
-    <hyperlink ref="O25" r:id="rId34"/>
-    <hyperlink ref="O26" r:id="rId35"/>
-    <hyperlink ref="O27" r:id="rId36"/>
-    <hyperlink ref="O28" r:id="rId37"/>
-    <hyperlink ref="O29" r:id="rId38"/>
-    <hyperlink ref="O32" r:id="rId39"/>
-    <hyperlink ref="O33" r:id="rId40"/>
-    <hyperlink ref="O35" r:id="rId41"/>
-    <hyperlink ref="O41" r:id="rId42"/>
-    <hyperlink ref="O43" r:id="rId43" display="LCSC"/>
-    <hyperlink ref="O44" r:id="rId44"/>
-    <hyperlink ref="O47" r:id="rId45"/>
-    <hyperlink ref="O57" r:id="rId46"/>
-    <hyperlink ref="O49" r:id="rId47"/>
-    <hyperlink ref="O50" r:id="rId48"/>
-    <hyperlink ref="O51" r:id="rId49"/>
-    <hyperlink ref="O60" r:id="rId50"/>
-    <hyperlink ref="O61" r:id="rId51"/>
-    <hyperlink ref="O62" r:id="rId52"/>
-    <hyperlink ref="O63" r:id="rId53"/>
-    <hyperlink ref="O64" r:id="rId54"/>
-    <hyperlink ref="O65" r:id="rId55"/>
-    <hyperlink ref="O67" r:id="rId56"/>
-    <hyperlink ref="O71" r:id="rId57"/>
-    <hyperlink ref="O72" r:id="rId58"/>
-    <hyperlink ref="O66" r:id="rId59"/>
-    <hyperlink ref="O11" r:id="rId60"/>
+    <hyperlink ref="O61" r:id="rId10"/>
+    <hyperlink ref="O55" r:id="rId11"/>
+    <hyperlink ref="O57" r:id="rId12"/>
+    <hyperlink ref="O56" r:id="rId13"/>
+    <hyperlink ref="O58" r:id="rId14"/>
+    <hyperlink ref="O59" r:id="rId15"/>
+    <hyperlink ref="O62" r:id="rId16"/>
+    <hyperlink ref="O38" r:id="rId17"/>
+    <hyperlink ref="O36" r:id="rId18"/>
+    <hyperlink ref="O33" r:id="rId19"/>
+    <hyperlink ref="O32" r:id="rId20"/>
+    <hyperlink ref="O40" r:id="rId21"/>
+    <hyperlink ref="O44" r:id="rId22"/>
+    <hyperlink ref="O47" r:id="rId23"/>
+    <hyperlink ref="O49" r:id="rId24"/>
+    <hyperlink ref="O25" r:id="rId25"/>
+    <hyperlink ref="O14" r:id="rId26"/>
+    <hyperlink ref="O15" r:id="rId27"/>
+    <hyperlink ref="O17" r:id="rId28"/>
+    <hyperlink ref="O19" r:id="rId29"/>
+    <hyperlink ref="O20" r:id="rId30"/>
+    <hyperlink ref="O21" r:id="rId31"/>
+    <hyperlink ref="O26" r:id="rId32"/>
+    <hyperlink ref="O27" r:id="rId33"/>
+    <hyperlink ref="O28" r:id="rId34"/>
+    <hyperlink ref="O29" r:id="rId35"/>
+    <hyperlink ref="O30" r:id="rId36"/>
+    <hyperlink ref="O31" r:id="rId37"/>
+    <hyperlink ref="O34" r:id="rId38"/>
+    <hyperlink ref="O35" r:id="rId39"/>
+    <hyperlink ref="O37" r:id="rId40"/>
+    <hyperlink ref="O43" r:id="rId41"/>
+    <hyperlink ref="O46" r:id="rId42"/>
+    <hyperlink ref="O50" r:id="rId43"/>
+    <hyperlink ref="O60" r:id="rId44"/>
+    <hyperlink ref="O52" r:id="rId45"/>
+    <hyperlink ref="O53" r:id="rId46"/>
+    <hyperlink ref="O54" r:id="rId47"/>
+    <hyperlink ref="O63" r:id="rId48"/>
+    <hyperlink ref="O64" r:id="rId49"/>
+    <hyperlink ref="O65" r:id="rId50"/>
+    <hyperlink ref="O66" r:id="rId51"/>
+    <hyperlink ref="O67" r:id="rId52"/>
+    <hyperlink ref="O68" r:id="rId53"/>
+    <hyperlink ref="O70" r:id="rId54"/>
+    <hyperlink ref="O74" r:id="rId55"/>
+    <hyperlink ref="O75" r:id="rId56"/>
+    <hyperlink ref="O69" r:id="rId57"/>
+    <hyperlink ref="O11" r:id="rId58"/>
+    <hyperlink ref="O39" r:id="rId59"/>
+    <hyperlink ref="O48" r:id="rId60"/>
+    <hyperlink ref="O45" r:id="rId61"/>
+    <hyperlink ref="O23" r:id="rId62"/>
+    <hyperlink ref="O24" r:id="rId63"/>
+    <hyperlink ref="O76" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId61"/>
-  <drawing r:id="rId62"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId65"/>
+  <drawing r:id="rId66"/>
 </worksheet>
 </file>
--- a/Design Files/LightSPT-Device-v1.0/BOM/eSpark_BOM_Light_spt_device.xlsx
+++ b/Design Files/LightSPT-Device-v1.0/BOM/eSpark_BOM_Light_spt_device.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="413">
   <si>
     <t>Component list</t>
   </si>
@@ -1252,6 +1252,12 @@
   </si>
   <si>
     <t>C497021</t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>USB Type A to A Cable</t>
   </si>
 </sst>
 </file>
@@ -1946,6 +1952,9 @@
     <xf numFmtId="0" fontId="24" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1977,9 +1986,6 @@
     <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2323,7 +2329,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z78"/>
+  <dimension ref="A1:Z79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -2360,15 +2366,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="79"/>
-      <c r="P1" s="79"/>
-      <c r="Q1" s="79"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="80"/>
+      <c r="O1" s="80"/>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="80"/>
+      <c r="R1" s="80"/>
+      <c r="S1" s="81"/>
     </row>
     <row r="2" spans="1:26" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2418,7 +2424,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="81"/>
+      <c r="S3" s="82"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2443,7 +2449,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="82"/>
+      <c r="S4" s="83"/>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2468,7 +2474,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="82"/>
+      <c r="S5" s="83"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2489,7 +2495,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="82"/>
+      <c r="S6" s="83"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2510,7 +2516,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="82"/>
+      <c r="S7" s="83"/>
     </row>
     <row r="8" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2531,7 +2537,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="82"/>
+      <c r="S8" s="83"/>
     </row>
     <row r="9" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -6279,9 +6285,9 @@
       <c r="R75" s="37"/>
       <c r="S75" s="39"/>
     </row>
-    <row r="76" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
-      <c r="B76" s="89">
+      <c r="B76" s="79">
         <v>67</v>
       </c>
       <c r="C76" s="54" t="s">
@@ -6334,65 +6340,114 @@
       <c r="R76" s="51"/>
       <c r="S76" s="59"/>
     </row>
-    <row r="77" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
-      <c r="B77" s="40"/>
-      <c r="C77" s="41"/>
-      <c r="D77" s="42"/>
-      <c r="E77" s="43"/>
-      <c r="F77" s="44"/>
-      <c r="G77" s="45"/>
-      <c r="H77" s="44"/>
-      <c r="I77" s="45"/>
-      <c r="J77" s="44"/>
-      <c r="K77" s="45"/>
-      <c r="L77" s="45"/>
-      <c r="M77" s="45"/>
-      <c r="N77" s="87" t="s">
+      <c r="B77" s="79">
+        <v>68</v>
+      </c>
+      <c r="C77" s="54" t="s">
+        <v>406</v>
+      </c>
+      <c r="D77" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="E77" s="51"/>
+      <c r="F77" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="G77" s="51" t="s">
+        <v>412</v>
+      </c>
+      <c r="H77" s="51"/>
+      <c r="I77" s="51" t="s">
+        <v>360</v>
+      </c>
+      <c r="J77" s="51"/>
+      <c r="K77" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="L77" s="51">
+        <v>1</v>
+      </c>
+      <c r="M77" s="51">
+        <f>L77*5</f>
         <v>5</v>
       </c>
-      <c r="O77" s="88"/>
-      <c r="P77" s="88"/>
-      <c r="Q77" s="48">
+      <c r="N77" s="51">
+        <v>6</v>
+      </c>
+      <c r="O77" s="63" t="s">
+        <v>411</v>
+      </c>
+      <c r="P77" s="52">
+        <v>2.38</v>
+      </c>
+      <c r="Q77" s="52">
+        <f>P77*N77</f>
+        <v>14.28</v>
+      </c>
+      <c r="R77" s="51"/>
+      <c r="S77" s="59"/>
+    </row>
+    <row r="78" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="1"/>
+      <c r="B78" s="40"/>
+      <c r="C78" s="41"/>
+      <c r="D78" s="42"/>
+      <c r="E78" s="43"/>
+      <c r="F78" s="44"/>
+      <c r="G78" s="45"/>
+      <c r="H78" s="44"/>
+      <c r="I78" s="45"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="45"/>
+      <c r="L78" s="45"/>
+      <c r="M78" s="45"/>
+      <c r="N78" s="88" t="s">
+        <v>5</v>
+      </c>
+      <c r="O78" s="89"/>
+      <c r="P78" s="89"/>
+      <c r="Q78" s="48">
         <f>SUM(Q10:Q76)</f>
         <v>276.32780000000002</v>
       </c>
-      <c r="R77" s="83"/>
-      <c r="S77" s="84"/>
-    </row>
-    <row r="78" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="1"/>
-      <c r="B78" s="25"/>
-      <c r="C78" s="36"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="10"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="10"/>
-      <c r="H78" s="10"/>
-      <c r="I78" s="10"/>
-      <c r="J78" s="10"/>
-      <c r="K78" s="10"/>
-      <c r="L78" s="10"/>
-      <c r="M78" s="10"/>
-      <c r="N78" s="87" t="s">
+      <c r="R78" s="84"/>
+      <c r="S78" s="85"/>
+    </row>
+    <row r="79" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="1"/>
+      <c r="B79" s="25"/>
+      <c r="C79" s="36"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="10"/>
+      <c r="F79" s="10"/>
+      <c r="G79" s="10"/>
+      <c r="H79" s="10"/>
+      <c r="I79" s="10"/>
+      <c r="J79" s="10"/>
+      <c r="K79" s="10"/>
+      <c r="L79" s="10"/>
+      <c r="M79" s="10"/>
+      <c r="N79" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="O78" s="88"/>
-      <c r="P78" s="88"/>
-      <c r="Q78" s="49">
-        <f>Q77/5</f>
+      <c r="O79" s="89"/>
+      <c r="P79" s="89"/>
+      <c r="Q79" s="49">
+        <f>Q78/5</f>
         <v>55.265560000000008</v>
       </c>
-      <c r="R78" s="85"/>
-      <c r="S78" s="86"/>
+      <c r="R79" s="86"/>
+      <c r="S79" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R77:S78"/>
-    <mergeCell ref="N77:P77"/>
+    <mergeCell ref="R78:S79"/>
     <mergeCell ref="N78:P78"/>
+    <mergeCell ref="N79:P79"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O18" r:id="rId1"/>
@@ -6459,9 +6514,10 @@
     <hyperlink ref="O23" r:id="rId62"/>
     <hyperlink ref="O24" r:id="rId63"/>
     <hyperlink ref="O76" r:id="rId64"/>
+    <hyperlink ref="O77" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId65"/>
-  <drawing r:id="rId66"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId66"/>
+  <drawing r:id="rId67"/>
 </worksheet>
 </file>